--- a/research/traditional_assets/database/data/singapore/singapore_utility_water.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_utility_water.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06417717306941925</v>
+        <v>0.06410542187520124</v>
       </c>
       <c r="C2">
-        <v>3360.67797950362</v>
+        <v>3329.81606141251</v>
       </c>
       <c r="D2">
-        <v>2965.577979503621</v>
+        <v>2968.705061412511</v>
       </c>
       <c r="E2">
-        <v>-3100.7</v>
+        <v>-3066.711</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33.989</v>
       </c>
       <c r="G2">
         <v>395.1</v>
@@ -1451,28 +1451,28 @@
         <v>342.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.7096467</v>
       </c>
       <c r="N2">
-        <v>342.775</v>
+        <v>341.0653533</v>
       </c>
       <c r="O2">
-        <v>58.27175</v>
+        <v>57.981110061</v>
       </c>
       <c r="P2">
-        <v>284.50325</v>
+        <v>283.084243239</v>
       </c>
       <c r="Q2">
-        <v>364.60325</v>
+        <v>363.184243239</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06417717306941925</v>
+        <v>0.06433124431838509</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.4279733098934201</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.4946402084127</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06410542187520124</v>
+        <v>0.06403367068098323</v>
       </c>
       <c r="C3">
-        <v>3329.81606141251</v>
+        <v>3298.960745045178</v>
       </c>
       <c r="D3">
-        <v>2968.705061412511</v>
+        <v>2971.838745045178</v>
       </c>
       <c r="E3">
-        <v>-3066.711</v>
+        <v>-3032.722</v>
       </c>
       <c r="F3">
-        <v>33.989</v>
+        <v>67.97799999999999</v>
       </c>
       <c r="G3">
         <v>395.1</v>
@@ -1533,28 +1533,28 @@
         <v>342.775</v>
       </c>
       <c r="M3">
-        <v>1.7096467</v>
+        <v>3.419293399999999</v>
       </c>
       <c r="N3">
-        <v>341.0653533</v>
+        <v>339.3557066</v>
       </c>
       <c r="O3">
-        <v>57.981110061</v>
+        <v>57.690470122</v>
       </c>
       <c r="P3">
-        <v>283.084243239</v>
+        <v>281.6652364779999</v>
       </c>
       <c r="Q3">
-        <v>363.184243239</v>
+        <v>361.765236478</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06433124431838509</v>
+        <v>0.06448845987855431</v>
       </c>
       <c r="T3">
-        <v>0.4279733098934201</v>
+        <v>0.4316041542391297</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.4946402084127</v>
+        <v>100.2473201042063</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06403367068098323</v>
+        <v>0.06396191948676522</v>
       </c>
       <c r="C4">
-        <v>3298.960745045178</v>
+        <v>3268.112051329509</v>
       </c>
       <c r="D4">
-        <v>2971.838745045178</v>
+        <v>2974.979051329509</v>
       </c>
       <c r="E4">
-        <v>-3032.722</v>
+        <v>-2998.733</v>
       </c>
       <c r="F4">
-        <v>67.97799999999999</v>
+        <v>101.967</v>
       </c>
       <c r="G4">
         <v>395.1</v>
@@ -1615,28 +1615,28 @@
         <v>342.775</v>
       </c>
       <c r="M4">
-        <v>3.419293399999999</v>
+        <v>5.128940099999999</v>
       </c>
       <c r="N4">
-        <v>339.3557066</v>
+        <v>337.6460599</v>
       </c>
       <c r="O4">
-        <v>57.690470122</v>
+        <v>57.399830183</v>
       </c>
       <c r="P4">
-        <v>281.6652364779999</v>
+        <v>280.2462297169999</v>
       </c>
       <c r="Q4">
-        <v>361.765236478</v>
+        <v>360.346229717</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06448845987855431</v>
+        <v>0.06464891699666517</v>
       </c>
       <c r="T4">
-        <v>0.4316041542391297</v>
+        <v>0.4353098613548538</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.2473201042063</v>
+        <v>66.83154673613755</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06396191948676522</v>
+        <v>0.06389016829254721</v>
       </c>
       <c r="C5">
-        <v>3268.112051329509</v>
+        <v>3237.27000128194</v>
       </c>
       <c r="D5">
-        <v>2974.979051329509</v>
+        <v>2978.126001281941</v>
       </c>
       <c r="E5">
-        <v>-2998.733</v>
+        <v>-2964.744</v>
       </c>
       <c r="F5">
-        <v>101.967</v>
+        <v>135.956</v>
       </c>
       <c r="G5">
         <v>395.1</v>
@@ -1697,28 +1697,28 @@
         <v>342.775</v>
       </c>
       <c r="M5">
-        <v>5.128940099999999</v>
+        <v>6.838586799999999</v>
       </c>
       <c r="N5">
-        <v>337.6460599</v>
+        <v>335.9364132</v>
       </c>
       <c r="O5">
-        <v>57.399830183</v>
+        <v>57.109190244</v>
       </c>
       <c r="P5">
-        <v>280.2462297169999</v>
+        <v>278.827222956</v>
       </c>
       <c r="Q5">
-        <v>360.346229717</v>
+        <v>358.927222956</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06464891699666517</v>
+        <v>0.06481271697140334</v>
       </c>
       <c r="T5">
-        <v>0.4353098613548538</v>
+        <v>0.4390927707021556</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.83154673613755</v>
+        <v>50.12366005210317</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06389016829254721</v>
+        <v>0.06381841709832918</v>
       </c>
       <c r="C6">
-        <v>3237.27000128194</v>
+        <v>3206.43461600793</v>
       </c>
       <c r="D6">
-        <v>2978.126001281941</v>
+        <v>2981.279616007931</v>
       </c>
       <c r="E6">
-        <v>-2964.744</v>
+        <v>-2930.755</v>
       </c>
       <c r="F6">
-        <v>135.956</v>
+        <v>169.945</v>
       </c>
       <c r="G6">
         <v>395.1</v>
@@ -1779,28 +1779,28 @@
         <v>342.775</v>
       </c>
       <c r="M6">
-        <v>6.838586799999999</v>
+        <v>8.548233499999998</v>
       </c>
       <c r="N6">
-        <v>335.9364132</v>
+        <v>334.2267665</v>
       </c>
       <c r="O6">
-        <v>57.109190244</v>
+        <v>56.818550305</v>
       </c>
       <c r="P6">
-        <v>278.827222956</v>
+        <v>277.408216195</v>
       </c>
       <c r="Q6">
-        <v>358.927222956</v>
+        <v>357.508216195</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06481271697140334</v>
+        <v>0.0649799653666623</v>
       </c>
       <c r="T6">
-        <v>0.4390927707021556</v>
+        <v>0.4429553202462426</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.12366005210317</v>
+        <v>40.09892804168253</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06381841709832918</v>
+        <v>0.06374666590411117</v>
       </c>
       <c r="C7">
-        <v>3206.43461600793</v>
+        <v>3175.605916702425</v>
       </c>
       <c r="D7">
-        <v>2981.279616007931</v>
+        <v>2984.439916702425</v>
       </c>
       <c r="E7">
-        <v>-2930.755</v>
+        <v>-2896.766</v>
       </c>
       <c r="F7">
-        <v>169.945</v>
+        <v>203.934</v>
       </c>
       <c r="G7">
         <v>395.1</v>
@@ -1861,28 +1861,28 @@
         <v>342.775</v>
       </c>
       <c r="M7">
-        <v>8.548233499999998</v>
+        <v>10.2578802</v>
       </c>
       <c r="N7">
-        <v>334.2267665</v>
+        <v>332.5171198</v>
       </c>
       <c r="O7">
-        <v>56.818550305</v>
+        <v>56.527910366</v>
       </c>
       <c r="P7">
-        <v>277.408216195</v>
+        <v>275.989209434</v>
       </c>
       <c r="Q7">
-        <v>357.508216195</v>
+        <v>356.089209434</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0649799653666623</v>
+        <v>0.06515077223841614</v>
       </c>
       <c r="T7">
-        <v>0.4429553202462426</v>
+        <v>0.446900051695523</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.09892804168253</v>
+        <v>33.41577336806878</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06374666590411117</v>
+        <v>0.06367491470989317</v>
       </c>
       <c r="C8">
-        <v>3175.605916702425</v>
+        <v>3144.783924650338</v>
       </c>
       <c r="D8">
-        <v>2984.439916702425</v>
+        <v>2987.606924650338</v>
       </c>
       <c r="E8">
-        <v>-2896.766</v>
+        <v>-2862.777</v>
       </c>
       <c r="F8">
-        <v>203.934</v>
+        <v>237.9229999999999</v>
       </c>
       <c r="G8">
         <v>395.1</v>
@@ -1943,28 +1943,28 @@
         <v>342.775</v>
       </c>
       <c r="M8">
-        <v>10.2578802</v>
+        <v>11.9675269</v>
       </c>
       <c r="N8">
-        <v>332.5171198</v>
+        <v>330.8074731</v>
       </c>
       <c r="O8">
-        <v>56.527910366</v>
+        <v>56.237270427</v>
       </c>
       <c r="P8">
-        <v>275.989209434</v>
+        <v>274.570202673</v>
       </c>
       <c r="Q8">
-        <v>356.089209434</v>
+        <v>354.670202673</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06515077223841614</v>
+        <v>0.06532525237622921</v>
       </c>
       <c r="T8">
-        <v>0.446900051695523</v>
+        <v>0.4509296160791965</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.41577336806878</v>
+        <v>28.64209145834467</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06367491470989317</v>
+        <v>0.06360316351567516</v>
       </c>
       <c r="C9">
-        <v>3144.783924650337</v>
+        <v>3113.968661227027</v>
       </c>
       <c r="D9">
-        <v>2987.606924650338</v>
+        <v>2990.780661227027</v>
       </c>
       <c r="E9">
-        <v>-2862.777</v>
+        <v>-2828.788</v>
       </c>
       <c r="F9">
-        <v>237.923</v>
+        <v>271.912</v>
       </c>
       <c r="G9">
         <v>395.1</v>
@@ -2025,28 +2025,28 @@
         <v>342.775</v>
       </c>
       <c r="M9">
-        <v>11.9675269</v>
+        <v>13.6771736</v>
       </c>
       <c r="N9">
-        <v>330.8074731</v>
+        <v>329.0978264</v>
       </c>
       <c r="O9">
-        <v>56.237270427</v>
+        <v>55.946630488</v>
       </c>
       <c r="P9">
-        <v>274.570202673</v>
+        <v>273.151195912</v>
       </c>
       <c r="Q9">
-        <v>354.670202673</v>
+        <v>353.251195912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06532525237622921</v>
+        <v>0.06550352556051647</v>
       </c>
       <c r="T9">
-        <v>0.4509296160791965</v>
+        <v>0.455046779688602</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.64209145834467</v>
+        <v>25.06183002605158</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06360316351567516</v>
+        <v>0.06353141232145713</v>
       </c>
       <c r="C10">
-        <v>3113.968661227027</v>
+        <v>3083.160147898777</v>
       </c>
       <c r="D10">
-        <v>2990.780661227027</v>
+        <v>2993.961147898777</v>
       </c>
       <c r="E10">
-        <v>-2828.788</v>
+        <v>-2794.799</v>
       </c>
       <c r="F10">
-        <v>271.912</v>
+        <v>305.901</v>
       </c>
       <c r="G10">
         <v>395.1</v>
@@ -2107,28 +2107,28 @@
         <v>342.775</v>
       </c>
       <c r="M10">
-        <v>13.6771736</v>
+        <v>15.3868203</v>
       </c>
       <c r="N10">
-        <v>329.0978264</v>
+        <v>327.3881797</v>
       </c>
       <c r="O10">
-        <v>55.946630488</v>
+        <v>55.65599054899999</v>
       </c>
       <c r="P10">
-        <v>273.151195912</v>
+        <v>271.7321891509999</v>
       </c>
       <c r="Q10">
-        <v>353.251195912</v>
+        <v>351.832189151</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06550352556051647</v>
+        <v>0.06568571683676608</v>
       </c>
       <c r="T10">
-        <v>0.455046779688602</v>
+        <v>0.4592544304103022</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.06183002605158</v>
+        <v>22.27718224537919</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06353141232145713</v>
+        <v>0.06345966112723912</v>
       </c>
       <c r="C11">
-        <v>3083.160147898777</v>
+        <v>3052.358406223275</v>
       </c>
       <c r="D11">
-        <v>2993.961147898777</v>
+        <v>2997.148406223275</v>
       </c>
       <c r="E11">
-        <v>-2794.799</v>
+        <v>-2760.81</v>
       </c>
       <c r="F11">
-        <v>305.901</v>
+        <v>339.8899999999999</v>
       </c>
       <c r="G11">
         <v>395.1</v>
@@ -2189,28 +2189,28 @@
         <v>342.775</v>
       </c>
       <c r="M11">
-        <v>15.3868203</v>
+        <v>17.096467</v>
       </c>
       <c r="N11">
-        <v>327.3881797</v>
+        <v>325.678533</v>
       </c>
       <c r="O11">
-        <v>55.65599054899999</v>
+        <v>55.36535061</v>
       </c>
       <c r="P11">
-        <v>271.7321891509999</v>
+        <v>270.31318239</v>
       </c>
       <c r="Q11">
-        <v>351.832189151</v>
+        <v>350.41318239</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06568571683676608</v>
+        <v>0.06587195680804347</v>
       </c>
       <c r="T11">
-        <v>0.4592544304103022</v>
+        <v>0.4635555844813735</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.27718224537919</v>
+        <v>20.04946402084127</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06345966112723912</v>
+        <v>0.06338790993302111</v>
       </c>
       <c r="C12">
-        <v>3052.358406223275</v>
+        <v>3021.563457850112</v>
       </c>
       <c r="D12">
-        <v>2997.148406223275</v>
+        <v>3000.342457850112</v>
       </c>
       <c r="E12">
-        <v>-2760.81</v>
+        <v>-2726.821</v>
       </c>
       <c r="F12">
-        <v>339.89</v>
+        <v>373.879</v>
       </c>
       <c r="G12">
         <v>395.1</v>
@@ -2271,28 +2271,28 @@
         <v>342.775</v>
       </c>
       <c r="M12">
-        <v>17.096467</v>
+        <v>18.8061137</v>
       </c>
       <c r="N12">
-        <v>325.678533</v>
+        <v>323.9688863</v>
       </c>
       <c r="O12">
-        <v>55.36535061</v>
+        <v>55.07471067100001</v>
       </c>
       <c r="P12">
-        <v>270.31318239</v>
+        <v>268.894175629</v>
       </c>
       <c r="Q12">
-        <v>350.41318239</v>
+        <v>348.994175629</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06587195680804347</v>
+        <v>0.06606238194721473</v>
       </c>
       <c r="T12">
-        <v>0.4635555844813735</v>
+        <v>0.4679533937001093</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.04946402084127</v>
+        <v>18.22678547349206</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06338790993302111</v>
+        <v>0.0633161587388031</v>
       </c>
       <c r="C13">
-        <v>3021.563457850112</v>
+        <v>2990.775324521258</v>
       </c>
       <c r="D13">
-        <v>3000.342457850112</v>
+        <v>3003.543324521258</v>
       </c>
       <c r="E13">
-        <v>-2726.821</v>
+        <v>-2692.832</v>
       </c>
       <c r="F13">
-        <v>373.879</v>
+        <v>407.8679999999999</v>
       </c>
       <c r="G13">
         <v>395.1</v>
@@ -2353,28 +2353,28 @@
         <v>342.775</v>
       </c>
       <c r="M13">
-        <v>18.8061137</v>
+        <v>20.51576039999999</v>
       </c>
       <c r="N13">
-        <v>323.9688863</v>
+        <v>322.2592396</v>
       </c>
       <c r="O13">
-        <v>55.07471067100001</v>
+        <v>54.784070732</v>
       </c>
       <c r="P13">
-        <v>268.894175629</v>
+        <v>267.475168868</v>
       </c>
       <c r="Q13">
-        <v>348.994175629</v>
+        <v>347.575168868</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06606238194721473</v>
+        <v>0.06625713493045807</v>
       </c>
       <c r="T13">
-        <v>0.4679533937001093</v>
+        <v>0.4724511531283619</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.22678547349206</v>
+        <v>16.70788668403439</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0633161587388031</v>
+        <v>0.06324440754458509</v>
       </c>
       <c r="C14">
-        <v>2990.775324521258</v>
+        <v>2959.994028071567</v>
       </c>
       <c r="D14">
-        <v>3003.543324521258</v>
+        <v>3006.751028071567</v>
       </c>
       <c r="E14">
-        <v>-2692.832</v>
+        <v>-2658.843</v>
       </c>
       <c r="F14">
-        <v>407.8679999999999</v>
+        <v>441.857</v>
       </c>
       <c r="G14">
         <v>395.1</v>
@@ -2435,28 +2435,28 @@
         <v>342.775</v>
       </c>
       <c r="M14">
-        <v>20.51576039999999</v>
+        <v>22.2254071</v>
       </c>
       <c r="N14">
-        <v>322.2592396</v>
+        <v>320.5495929</v>
       </c>
       <c r="O14">
-        <v>54.784070732</v>
+        <v>54.493430793</v>
       </c>
       <c r="P14">
-        <v>267.475168868</v>
+        <v>266.056162107</v>
       </c>
       <c r="Q14">
-        <v>347.575168868</v>
+        <v>346.156162107</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06625713493045807</v>
+        <v>0.06645636499377597</v>
       </c>
       <c r="T14">
-        <v>0.4724511531283619</v>
+        <v>0.47705230932508</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.70788668403439</v>
+        <v>15.42266463141636</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06324440754458509</v>
+        <v>0.06317265635036706</v>
       </c>
       <c r="C15">
-        <v>2959.994028071567</v>
+        <v>2929.219590429268</v>
       </c>
       <c r="D15">
-        <v>3006.751028071567</v>
+        <v>3009.965590429268</v>
       </c>
       <c r="E15">
-        <v>-2658.843</v>
+        <v>-2624.854</v>
       </c>
       <c r="F15">
-        <v>441.857</v>
+        <v>475.846</v>
       </c>
       <c r="G15">
         <v>395.1</v>
@@ -2517,28 +2517,28 @@
         <v>342.775</v>
       </c>
       <c r="M15">
-        <v>22.2254071</v>
+        <v>23.9350538</v>
       </c>
       <c r="N15">
-        <v>320.5495929</v>
+        <v>318.8399462</v>
       </c>
       <c r="O15">
-        <v>54.493430793</v>
+        <v>54.202790854</v>
       </c>
       <c r="P15">
-        <v>266.056162107</v>
+        <v>264.637155346</v>
       </c>
       <c r="Q15">
-        <v>346.156162107</v>
+        <v>344.737155346</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06645636499377597</v>
+        <v>0.06666022831438032</v>
       </c>
       <c r="T15">
-        <v>0.47705230932508</v>
+        <v>0.4817604691542799</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.42266463141636</v>
+        <v>14.32104572917233</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06317265635036706</v>
+        <v>0.06310090515614905</v>
       </c>
       <c r="C16">
-        <v>2929.219590429268</v>
+        <v>2898.452033616464</v>
       </c>
       <c r="D16">
-        <v>3009.965590429268</v>
+        <v>3013.187033616464</v>
       </c>
       <c r="E16">
-        <v>-2624.854</v>
+        <v>-2590.865</v>
       </c>
       <c r="F16">
-        <v>475.846</v>
+        <v>509.835</v>
       </c>
       <c r="G16">
         <v>395.1</v>
@@ -2599,28 +2599,28 @@
         <v>342.775</v>
       </c>
       <c r="M16">
-        <v>23.9350538</v>
+        <v>25.6447005</v>
       </c>
       <c r="N16">
-        <v>318.8399462</v>
+        <v>317.1302995</v>
       </c>
       <c r="O16">
-        <v>54.202790854</v>
+        <v>53.912150915</v>
       </c>
       <c r="P16">
-        <v>264.637155346</v>
+        <v>263.218148585</v>
       </c>
       <c r="Q16">
-        <v>344.737155346</v>
+        <v>343.318148585</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06666022831438032</v>
+        <v>0.06686888841899889</v>
       </c>
       <c r="T16">
-        <v>0.4817604691542799</v>
+        <v>0.4865794092147551</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.32104572917233</v>
+        <v>13.36630934722751</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06310090515614905</v>
+        <v>0.06322835396193105</v>
       </c>
       <c r="C17">
-        <v>2898.452033616464</v>
+        <v>2858.745656531946</v>
       </c>
       <c r="D17">
-        <v>3013.187033616464</v>
+        <v>3007.469656531946</v>
       </c>
       <c r="E17">
-        <v>-2590.865</v>
+        <v>-2556.876</v>
       </c>
       <c r="F17">
-        <v>509.8349999999999</v>
+        <v>543.824</v>
       </c>
       <c r="G17">
         <v>395.1</v>
@@ -2681,45 +2681,45 @@
         <v>342.775</v>
       </c>
       <c r="M17">
-        <v>25.6447005</v>
+        <v>28.1700832</v>
       </c>
       <c r="N17">
-        <v>317.1302995</v>
+        <v>314.6049168</v>
       </c>
       <c r="O17">
-        <v>53.912150915</v>
+        <v>53.48283585599999</v>
       </c>
       <c r="P17">
-        <v>263.218148585</v>
+        <v>261.1220809439999</v>
       </c>
       <c r="Q17">
-        <v>343.318148585</v>
+        <v>341.222080944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.06686888841899889</v>
+        <v>0.06708251662134648</v>
       </c>
       <c r="T17">
-        <v>0.4865794092147551</v>
+        <v>0.4915130859433369</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.17</v>
       </c>
       <c r="W17">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.36630934722751</v>
+        <v>12.16805067867176</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06322835396193105</v>
+        <v>0.06316905276771304</v>
       </c>
       <c r="C18">
-        <v>2858.745656531946</v>
+        <v>2827.414217682101</v>
       </c>
       <c r="D18">
-        <v>3007.469656531946</v>
+        <v>3010.127217682101</v>
       </c>
       <c r="E18">
-        <v>-2556.876</v>
+        <v>-2522.887</v>
       </c>
       <c r="F18">
-        <v>543.824</v>
+        <v>577.813</v>
       </c>
       <c r="G18">
         <v>395.1</v>
@@ -2763,28 +2763,28 @@
         <v>342.775</v>
       </c>
       <c r="M18">
-        <v>28.1700832</v>
+        <v>29.9307134</v>
       </c>
       <c r="N18">
-        <v>314.6049168</v>
+        <v>312.8442866</v>
       </c>
       <c r="O18">
-        <v>53.48283585599999</v>
+        <v>53.183528722</v>
       </c>
       <c r="P18">
-        <v>261.1220809439999</v>
+        <v>259.660757878</v>
       </c>
       <c r="Q18">
-        <v>341.222080944</v>
+        <v>339.760757878</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06708251662134648</v>
+        <v>0.06730129249122052</v>
       </c>
       <c r="T18">
-        <v>0.4915130859433369</v>
+        <v>0.496565646448511</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.16805067867176</v>
+        <v>11.45228299169107</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06316905276771304</v>
+        <v>0.06310975157349502</v>
       </c>
       <c r="C19">
-        <v>2827.414217682101</v>
+        <v>2796.087479712739</v>
       </c>
       <c r="D19">
-        <v>3010.127217682101</v>
+        <v>3012.789479712739</v>
       </c>
       <c r="E19">
-        <v>-2522.887</v>
+        <v>-2488.898</v>
       </c>
       <c r="F19">
-        <v>577.813</v>
+        <v>611.802</v>
       </c>
       <c r="G19">
         <v>395.1</v>
@@ -2845,28 +2845,28 @@
         <v>342.775</v>
       </c>
       <c r="M19">
-        <v>29.9307134</v>
+        <v>31.6913436</v>
       </c>
       <c r="N19">
-        <v>312.8442866</v>
+        <v>311.0836564</v>
       </c>
       <c r="O19">
-        <v>53.183528722</v>
+        <v>52.884221588</v>
       </c>
       <c r="P19">
-        <v>259.660757878</v>
+        <v>258.199434812</v>
       </c>
       <c r="Q19">
-        <v>339.760757878</v>
+        <v>338.299434812</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.06730129249122052</v>
+        <v>0.06752540435792076</v>
       </c>
       <c r="T19">
-        <v>0.496565646448511</v>
+        <v>0.501741440136738</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.45228299169107</v>
+        <v>10.81604504770823</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06310975157349502</v>
+        <v>0.06305045037927701</v>
       </c>
       <c r="C20">
-        <v>2796.087479712739</v>
+        <v>2764.76545510777</v>
       </c>
       <c r="D20">
-        <v>3012.789479712739</v>
+        <v>3015.45645510777</v>
       </c>
       <c r="E20">
-        <v>-2488.898</v>
+        <v>-2454.909</v>
       </c>
       <c r="F20">
-        <v>611.8019999999999</v>
+        <v>645.7909999999999</v>
       </c>
       <c r="G20">
         <v>395.1</v>
@@ -2927,28 +2927,28 @@
         <v>342.775</v>
       </c>
       <c r="M20">
-        <v>31.6913436</v>
+        <v>33.4519738</v>
       </c>
       <c r="N20">
-        <v>311.0836564</v>
+        <v>309.3230262</v>
       </c>
       <c r="O20">
-        <v>52.884221588</v>
+        <v>52.584914454</v>
       </c>
       <c r="P20">
-        <v>258.199434812</v>
+        <v>256.738111746</v>
       </c>
       <c r="Q20">
-        <v>338.299434812</v>
+        <v>336.838111746</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06752540435792076</v>
+        <v>0.06775504985095927</v>
       </c>
       <c r="T20">
-        <v>0.501741440136738</v>
+        <v>0.5070450311999832</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.81604504770823</v>
+        <v>10.24677951888148</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06305045037927701</v>
+        <v>0.063273349185059</v>
       </c>
       <c r="C21">
-        <v>2764.76545510777</v>
+        <v>2720.776341158808</v>
       </c>
       <c r="D21">
-        <v>3015.45645510777</v>
+        <v>3005.456341158808</v>
       </c>
       <c r="E21">
-        <v>-2454.909</v>
+        <v>-2420.92</v>
       </c>
       <c r="F21">
-        <v>645.7909999999999</v>
+        <v>679.78</v>
       </c>
       <c r="G21">
         <v>395.1</v>
@@ -3009,45 +3009,45 @@
         <v>342.775</v>
       </c>
       <c r="M21">
-        <v>33.4519738</v>
+        <v>36.36823</v>
       </c>
       <c r="N21">
-        <v>309.3230262</v>
+        <v>306.40677</v>
       </c>
       <c r="O21">
-        <v>52.584914454</v>
+        <v>52.0891509</v>
       </c>
       <c r="P21">
-        <v>256.738111746</v>
+        <v>254.3176191</v>
       </c>
       <c r="Q21">
-        <v>336.838111746</v>
+        <v>334.4176191</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06775504985095927</v>
+        <v>0.06799043648132375</v>
       </c>
       <c r="T21">
-        <v>0.5070450311999832</v>
+        <v>0.5124812120398095</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.17</v>
       </c>
       <c r="W21">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.24677951888148</v>
+        <v>9.425121871479586</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.063273349185059</v>
+        <v>0.06322815799084099</v>
       </c>
       <c r="C22">
-        <v>2720.776341158808</v>
+        <v>2688.809431175958</v>
       </c>
       <c r="D22">
-        <v>3005.456341158808</v>
+        <v>3007.478431175958</v>
       </c>
       <c r="E22">
-        <v>-2420.92</v>
+        <v>-2386.931</v>
       </c>
       <c r="F22">
-        <v>679.78</v>
+        <v>713.769</v>
       </c>
       <c r="G22">
         <v>395.1</v>
@@ -3091,28 +3091,28 @@
         <v>342.775</v>
       </c>
       <c r="M22">
-        <v>36.36823</v>
+        <v>38.1866415</v>
       </c>
       <c r="N22">
-        <v>306.40677</v>
+        <v>304.5883585</v>
       </c>
       <c r="O22">
-        <v>52.0891509</v>
+        <v>51.780020945</v>
       </c>
       <c r="P22">
-        <v>254.3176191</v>
+        <v>252.808337555</v>
       </c>
       <c r="Q22">
-        <v>334.4176191</v>
+        <v>332.908337555</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06799043648132375</v>
+        <v>0.06823178226688732</v>
       </c>
       <c r="T22">
-        <v>0.5124812120398095</v>
+        <v>0.5180550177110236</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.425121871479586</v>
+        <v>8.976306544266272</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06322815799084099</v>
+        <v>0.06318296679662297</v>
       </c>
       <c r="C23">
-        <v>2688.809431175958</v>
+        <v>2656.845243974893</v>
       </c>
       <c r="D23">
-        <v>3007.478431175958</v>
+        <v>3009.503243974892</v>
       </c>
       <c r="E23">
-        <v>-2386.931</v>
+        <v>-2352.942</v>
       </c>
       <c r="F23">
-        <v>713.7689999999999</v>
+        <v>747.7579999999999</v>
       </c>
       <c r="G23">
         <v>395.1</v>
@@ -3173,28 +3173,28 @@
         <v>342.775</v>
       </c>
       <c r="M23">
-        <v>38.18664149999999</v>
+        <v>40.005053</v>
       </c>
       <c r="N23">
-        <v>304.5883585</v>
+        <v>302.769947</v>
       </c>
       <c r="O23">
-        <v>51.780020945</v>
+        <v>51.47089099</v>
       </c>
       <c r="P23">
-        <v>252.808337555</v>
+        <v>251.29905601</v>
       </c>
       <c r="Q23">
-        <v>332.908337555</v>
+        <v>331.39905601</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06823178226688732</v>
+        <v>0.06847931640592689</v>
       </c>
       <c r="T23">
-        <v>0.5180550177110236</v>
+        <v>0.5237717414763715</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.976306544266272</v>
+        <v>8.568292610435988</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06318296679662297</v>
+        <v>0.06313777560240497</v>
       </c>
       <c r="C24">
-        <v>2656.845243974893</v>
+        <v>2624.883785058733</v>
       </c>
       <c r="D24">
-        <v>3009.503243974892</v>
+        <v>3011.530785058733</v>
       </c>
       <c r="E24">
-        <v>-2352.942</v>
+        <v>-2318.953</v>
       </c>
       <c r="F24">
-        <v>747.7579999999999</v>
+        <v>781.747</v>
       </c>
       <c r="G24">
         <v>395.1</v>
@@ -3255,28 +3255,28 @@
         <v>342.775</v>
       </c>
       <c r="M24">
-        <v>40.005053</v>
+        <v>41.8234645</v>
       </c>
       <c r="N24">
-        <v>302.769947</v>
+        <v>300.9515355</v>
       </c>
       <c r="O24">
-        <v>51.47089099</v>
+        <v>51.161761035</v>
       </c>
       <c r="P24">
-        <v>251.29905601</v>
+        <v>249.789774465</v>
       </c>
       <c r="Q24">
-        <v>331.39905601</v>
+        <v>329.889774465</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06847931640592689</v>
+        <v>0.06873328000312333</v>
       </c>
       <c r="T24">
-        <v>0.5237717414763715</v>
+        <v>0.5296369515732869</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.568292610435988</v>
+        <v>8.195758149112683</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06313777560240497</v>
+        <v>0.06309258440818695</v>
       </c>
       <c r="C25">
-        <v>2624.883785058733</v>
+        <v>2592.925059945439</v>
       </c>
       <c r="D25">
-        <v>3011.530785058733</v>
+        <v>3013.561059945439</v>
       </c>
       <c r="E25">
-        <v>-2318.953</v>
+        <v>-2284.964</v>
       </c>
       <c r="F25">
-        <v>781.747</v>
+        <v>815.736</v>
       </c>
       <c r="G25">
         <v>395.1</v>
@@ -3337,28 +3337,28 @@
         <v>342.775</v>
       </c>
       <c r="M25">
-        <v>41.8234645</v>
+        <v>43.641876</v>
       </c>
       <c r="N25">
-        <v>300.9515355</v>
+        <v>299.133124</v>
       </c>
       <c r="O25">
-        <v>51.161761035</v>
+        <v>50.85263107999999</v>
       </c>
       <c r="P25">
-        <v>249.789774465</v>
+        <v>248.28049292</v>
       </c>
       <c r="Q25">
-        <v>329.889774465</v>
+        <v>328.38049292</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.06873328000312333</v>
+        <v>0.06899392685287756</v>
       </c>
       <c r="T25">
-        <v>0.5296369515732869</v>
+        <v>0.5356565093043316</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.195758149112683</v>
+        <v>7.854268226232987</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06309258440818695</v>
+        <v>0.06321339321396893</v>
       </c>
       <c r="C26">
-        <v>2592.925059945439</v>
+        <v>2553.514674239436</v>
       </c>
       <c r="D26">
-        <v>3013.561059945439</v>
+        <v>3008.139674239436</v>
       </c>
       <c r="E26">
-        <v>-2284.964</v>
+        <v>-2250.975</v>
       </c>
       <c r="F26">
-        <v>815.7359999999999</v>
+        <v>849.7249999999999</v>
       </c>
       <c r="G26">
         <v>395.1</v>
@@ -3419,45 +3419,45 @@
         <v>342.775</v>
       </c>
       <c r="M26">
-        <v>43.64187599999999</v>
+        <v>46.14006749999999</v>
       </c>
       <c r="N26">
-        <v>299.133124</v>
+        <v>296.6349325</v>
       </c>
       <c r="O26">
-        <v>50.85263108</v>
+        <v>50.427938525</v>
       </c>
       <c r="P26">
-        <v>248.28049292</v>
+        <v>246.206993975</v>
       </c>
       <c r="Q26">
-        <v>328.3804929200001</v>
+        <v>326.306993975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06899392685287756</v>
+        <v>0.06926152428529191</v>
       </c>
       <c r="T26">
-        <v>0.5356565093043316</v>
+        <v>0.5418365885748709</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.17</v>
       </c>
       <c r="W26">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.85426822623299</v>
+        <v>7.429009504591645</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06321339321396893</v>
+        <v>0.06317484201975092</v>
       </c>
       <c r="C27">
-        <v>2553.514674239436</v>
+        <v>2521.253567628098</v>
       </c>
       <c r="D27">
-        <v>3008.139674239436</v>
+        <v>3009.867567628098</v>
       </c>
       <c r="E27">
-        <v>-2250.975</v>
+        <v>-2216.986</v>
       </c>
       <c r="F27">
-        <v>849.7249999999999</v>
+        <v>883.7139999999999</v>
       </c>
       <c r="G27">
         <v>395.1</v>
@@ -3501,28 +3501,28 @@
         <v>342.775</v>
       </c>
       <c r="M27">
-        <v>46.14006749999999</v>
+        <v>47.9856702</v>
       </c>
       <c r="N27">
-        <v>296.6349325</v>
+        <v>294.7893298</v>
       </c>
       <c r="O27">
-        <v>50.427938525</v>
+        <v>50.11418606599999</v>
       </c>
       <c r="P27">
-        <v>246.206993975</v>
+        <v>244.675143734</v>
       </c>
       <c r="Q27">
-        <v>326.306993975</v>
+        <v>324.775143734</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.06926152428529191</v>
+        <v>0.06953635408074449</v>
       </c>
       <c r="T27">
-        <v>0.5418365885748709</v>
+        <v>0.5481836970148842</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.429009504591645</v>
+        <v>7.143278369799656</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06317484201975092</v>
+        <v>0.0631362908255329</v>
       </c>
       <c r="C28">
-        <v>2521.253567628098</v>
+        <v>2488.994447182181</v>
       </c>
       <c r="D28">
-        <v>3009.867567628098</v>
+        <v>3011.597447182181</v>
       </c>
       <c r="E28">
-        <v>-2216.986</v>
+        <v>-2182.997</v>
       </c>
       <c r="F28">
-        <v>883.7139999999999</v>
+        <v>917.703</v>
       </c>
       <c r="G28">
         <v>395.1</v>
@@ -3583,28 +3583,28 @@
         <v>342.775</v>
       </c>
       <c r="M28">
-        <v>47.9856702</v>
+        <v>49.8312729</v>
       </c>
       <c r="N28">
-        <v>294.7893298</v>
+        <v>292.9437271</v>
       </c>
       <c r="O28">
-        <v>50.11418606599999</v>
+        <v>49.800433607</v>
       </c>
       <c r="P28">
-        <v>244.675143734</v>
+        <v>243.143293493</v>
       </c>
       <c r="Q28">
-        <v>324.775143734</v>
+        <v>323.243293493</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.06953635408074449</v>
+        <v>0.06981871345963411</v>
       </c>
       <c r="T28">
-        <v>0.5481836970148842</v>
+        <v>0.5547046988368157</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.143278369799656</v>
+        <v>6.878712504251522</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0631362908255329</v>
+        <v>0.06309773963131489</v>
       </c>
       <c r="C29">
-        <v>2488.994447182181</v>
+        <v>2456.73731632822</v>
       </c>
       <c r="D29">
-        <v>3011.597447182181</v>
+        <v>3013.329316328221</v>
       </c>
       <c r="E29">
-        <v>-2182.997</v>
+        <v>-2149.008</v>
       </c>
       <c r="F29">
-        <v>917.703</v>
+        <v>951.692</v>
       </c>
       <c r="G29">
         <v>395.1</v>
@@ -3665,28 +3665,28 @@
         <v>342.775</v>
       </c>
       <c r="M29">
-        <v>49.8312729</v>
+        <v>51.6768756</v>
       </c>
       <c r="N29">
-        <v>292.9437271</v>
+        <v>291.0981244</v>
       </c>
       <c r="O29">
-        <v>49.800433607</v>
+        <v>49.486681148</v>
       </c>
       <c r="P29">
-        <v>243.143293493</v>
+        <v>241.611443252</v>
       </c>
       <c r="Q29">
-        <v>323.243293493</v>
+        <v>321.711443252</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.06981871345963411</v>
+        <v>0.07010891615460402</v>
       </c>
       <c r="T29">
-        <v>0.5547046988368157</v>
+        <v>0.5614068395982453</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.878712504251522</v>
+        <v>6.633044200528253</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06309773963131489</v>
+        <v>0.06305918843709689</v>
       </c>
       <c r="C30">
-        <v>2456.73731632822</v>
+        <v>2424.482178500633</v>
       </c>
       <c r="D30">
-        <v>3013.329316328221</v>
+        <v>3015.063178500633</v>
       </c>
       <c r="E30">
-        <v>-2149.008</v>
+        <v>-2115.019</v>
       </c>
       <c r="F30">
-        <v>951.692</v>
+        <v>985.681</v>
       </c>
       <c r="G30">
         <v>395.1</v>
@@ -3747,28 +3747,28 @@
         <v>342.775</v>
       </c>
       <c r="M30">
-        <v>51.6768756</v>
+        <v>53.5224783</v>
       </c>
       <c r="N30">
-        <v>291.0981244</v>
+        <v>289.2525217</v>
       </c>
       <c r="O30">
-        <v>49.486681148</v>
+        <v>49.172928689</v>
       </c>
       <c r="P30">
-        <v>241.611443252</v>
+        <v>240.079593011</v>
       </c>
       <c r="Q30">
-        <v>321.711443252</v>
+        <v>320.179593011</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07010891615460402</v>
+        <v>0.0704072935733759</v>
       </c>
       <c r="T30">
-        <v>0.5614068395982453</v>
+        <v>0.56829777305718</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.633044200528253</v>
+        <v>6.404318538441071</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06305918843709687</v>
+        <v>0.06302063724287887</v>
       </c>
       <c r="C31">
-        <v>2424.482178500633</v>
+        <v>2392.229037141747</v>
       </c>
       <c r="D31">
-        <v>3015.063178500633</v>
+        <v>3016.799037141747</v>
       </c>
       <c r="E31">
-        <v>-2115.019</v>
+        <v>-2081.03</v>
       </c>
       <c r="F31">
-        <v>985.6809999999998</v>
+        <v>1019.67</v>
       </c>
       <c r="G31">
         <v>395.1</v>
@@ -3829,28 +3829,28 @@
         <v>342.775</v>
       </c>
       <c r="M31">
-        <v>53.52247829999999</v>
+        <v>55.36808099999999</v>
       </c>
       <c r="N31">
-        <v>289.2525217</v>
+        <v>287.406919</v>
       </c>
       <c r="O31">
-        <v>49.172928689</v>
+        <v>48.85917623</v>
       </c>
       <c r="P31">
-        <v>240.079593011</v>
+        <v>238.54774277</v>
       </c>
       <c r="Q31">
-        <v>320.179593011</v>
+        <v>318.64774277</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0704072935733759</v>
+        <v>0.07071419606125554</v>
       </c>
       <c r="T31">
-        <v>0.56829777305718</v>
+        <v>0.575385590329227</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.404318538441073</v>
+        <v>6.190841253826371</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06302063724287887</v>
+        <v>0.06323938604866085</v>
       </c>
       <c r="C32">
-        <v>2392.229037141747</v>
+        <v>2348.416775242738</v>
       </c>
       <c r="D32">
-        <v>3016.799037141747</v>
+        <v>3006.975775242738</v>
       </c>
       <c r="E32">
-        <v>-2081.03</v>
+        <v>-2047.041</v>
       </c>
       <c r="F32">
-        <v>1019.67</v>
+        <v>1053.659</v>
       </c>
       <c r="G32">
         <v>395.1</v>
@@ -3911,45 +3911,45 @@
         <v>342.775</v>
       </c>
       <c r="M32">
-        <v>55.36808099999999</v>
+        <v>58.26734269999999</v>
       </c>
       <c r="N32">
-        <v>287.406919</v>
+        <v>284.5076573</v>
       </c>
       <c r="O32">
-        <v>48.85917623</v>
+        <v>48.366301741</v>
       </c>
       <c r="P32">
-        <v>238.54774277</v>
+        <v>236.141355559</v>
       </c>
       <c r="Q32">
-        <v>318.64774277</v>
+        <v>316.241355559</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07071419606125554</v>
+        <v>0.07102999427342153</v>
       </c>
       <c r="T32">
-        <v>0.575385590329227</v>
+        <v>0.582678851580174</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.17</v>
       </c>
       <c r="W32">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.190841253826371</v>
+        <v>5.882797878132857</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06323938604866085</v>
+        <v>0.06320913485444285</v>
       </c>
       <c r="C33">
-        <v>2348.416775242738</v>
+        <v>2315.782439628744</v>
       </c>
       <c r="D33">
-        <v>3006.975775242738</v>
+        <v>3008.330439628744</v>
       </c>
       <c r="E33">
-        <v>-2047.041</v>
+        <v>-2013.052</v>
       </c>
       <c r="F33">
-        <v>1053.659</v>
+        <v>1087.648</v>
       </c>
       <c r="G33">
         <v>395.1</v>
@@ -3993,28 +3993,28 @@
         <v>342.775</v>
       </c>
       <c r="M33">
-        <v>58.26734269999999</v>
+        <v>60.1469344</v>
       </c>
       <c r="N33">
-        <v>284.5076573</v>
+        <v>282.6280656</v>
       </c>
       <c r="O33">
-        <v>48.366301741</v>
+        <v>48.046771152</v>
       </c>
       <c r="P33">
-        <v>236.141355559</v>
+        <v>234.581294448</v>
       </c>
       <c r="Q33">
-        <v>316.241355559</v>
+        <v>314.681294448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07102999427342153</v>
+        <v>0.07135508066829831</v>
       </c>
       <c r="T33">
-        <v>0.582678851580174</v>
+        <v>0.5901866205149724</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.882797878132857</v>
+        <v>5.698960444441204</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06320913485444285</v>
+        <v>0.06317888366022484</v>
       </c>
       <c r="C34">
-        <v>2315.782439628744</v>
+        <v>2283.149325137128</v>
       </c>
       <c r="D34">
-        <v>3008.330439628744</v>
+        <v>3009.686325137128</v>
       </c>
       <c r="E34">
-        <v>-2013.052</v>
+        <v>-1979.063</v>
       </c>
       <c r="F34">
-        <v>1087.648</v>
+        <v>1121.637</v>
       </c>
       <c r="G34">
         <v>395.1</v>
@@ -4075,28 +4075,28 @@
         <v>342.775</v>
       </c>
       <c r="M34">
-        <v>60.1469344</v>
+        <v>62.0265261</v>
       </c>
       <c r="N34">
-        <v>282.6280656</v>
+        <v>280.7484739</v>
       </c>
       <c r="O34">
-        <v>48.046771152</v>
+        <v>47.727240563</v>
       </c>
       <c r="P34">
-        <v>234.581294448</v>
+        <v>233.021233337</v>
       </c>
       <c r="Q34">
-        <v>314.681294448</v>
+        <v>313.121233337</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07135508066829831</v>
+        <v>0.07168987113466394</v>
       </c>
       <c r="T34">
-        <v>0.5901866205149724</v>
+        <v>0.5979185019552872</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.698960444441204</v>
+        <v>5.526264673397532</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06317888366022484</v>
+        <v>0.06314863246600683</v>
       </c>
       <c r="C35">
-        <v>2283.149325137128</v>
+        <v>2250.517433419752</v>
       </c>
       <c r="D35">
-        <v>3009.686325137128</v>
+        <v>3011.043433419752</v>
       </c>
       <c r="E35">
-        <v>-1979.063</v>
+        <v>-1945.074</v>
       </c>
       <c r="F35">
-        <v>1121.637</v>
+        <v>1155.626</v>
       </c>
       <c r="G35">
         <v>395.1</v>
@@ -4157,28 +4157,28 @@
         <v>342.775</v>
       </c>
       <c r="M35">
-        <v>62.0265261</v>
+        <v>63.9061178</v>
       </c>
       <c r="N35">
-        <v>280.7484739</v>
+        <v>278.8688822</v>
       </c>
       <c r="O35">
-        <v>47.727240563</v>
+        <v>47.407709974</v>
       </c>
       <c r="P35">
-        <v>233.021233337</v>
+        <v>231.461172226</v>
       </c>
       <c r="Q35">
-        <v>313.121233337</v>
+        <v>311.561172226</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07168987113466394</v>
+        <v>0.07203480676667701</v>
       </c>
       <c r="T35">
-        <v>0.5979185019552872</v>
+        <v>0.6058846828331871</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.526264673397532</v>
+        <v>5.363727477121134</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06314863246600683</v>
+        <v>0.0631183812717888</v>
       </c>
       <c r="C36">
-        <v>2250.517433419752</v>
+        <v>2217.886766131459</v>
       </c>
       <c r="D36">
-        <v>3011.043433419752</v>
+        <v>3012.401766131459</v>
       </c>
       <c r="E36">
-        <v>-1945.074</v>
+        <v>-1911.085</v>
       </c>
       <c r="F36">
-        <v>1155.626</v>
+        <v>1189.615</v>
       </c>
       <c r="G36">
         <v>395.1</v>
@@ -4239,28 +4239,28 @@
         <v>342.775</v>
       </c>
       <c r="M36">
-        <v>63.9061178</v>
+        <v>65.7857095</v>
       </c>
       <c r="N36">
-        <v>278.8688822</v>
+        <v>276.9892905</v>
       </c>
       <c r="O36">
-        <v>47.407709974</v>
+        <v>47.088179385</v>
       </c>
       <c r="P36">
-        <v>231.461172226</v>
+        <v>229.901111115</v>
       </c>
       <c r="Q36">
-        <v>311.561172226</v>
+        <v>310.001111115</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07203480676667701</v>
+        <v>0.07239035580275201</v>
       </c>
       <c r="T36">
-        <v>0.6058846828331871</v>
+        <v>0.6140959769688686</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.363727477121134</v>
+        <v>5.210478120631959</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0631183812717888</v>
+        <v>0.06308813007757079</v>
       </c>
       <c r="C37">
-        <v>2217.886766131459</v>
+        <v>2185.257324930077</v>
       </c>
       <c r="D37">
-        <v>3012.401766131459</v>
+        <v>3013.761324930077</v>
       </c>
       <c r="E37">
-        <v>-1911.085</v>
+        <v>-1877.096</v>
       </c>
       <c r="F37">
-        <v>1189.615</v>
+        <v>1223.604</v>
       </c>
       <c r="G37">
         <v>395.1</v>
@@ -4321,28 +4321,28 @@
         <v>342.775</v>
       </c>
       <c r="M37">
-        <v>65.7857095</v>
+        <v>67.6653012</v>
       </c>
       <c r="N37">
-        <v>276.9892905</v>
+        <v>275.1096988</v>
       </c>
       <c r="O37">
-        <v>47.088179385</v>
+        <v>46.768648796</v>
       </c>
       <c r="P37">
-        <v>229.901111115</v>
+        <v>228.341050004</v>
       </c>
       <c r="Q37">
-        <v>310.001111115</v>
+        <v>308.441050004</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07239035580275201</v>
+        <v>0.07275701574620437</v>
       </c>
       <c r="T37">
-        <v>0.6140959769688686</v>
+        <v>0.6225638740462903</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.210478120631959</v>
+        <v>5.065742617281071</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0630881300775708</v>
+        <v>0.06305787888335278</v>
       </c>
       <c r="C38">
-        <v>2185.257324930076</v>
+        <v>2152.62911147643</v>
       </c>
       <c r="D38">
-        <v>3013.761324930076</v>
+        <v>3015.12211147643</v>
       </c>
       <c r="E38">
-        <v>-1877.096</v>
+        <v>-1843.107</v>
       </c>
       <c r="F38">
-        <v>1223.604</v>
+        <v>1257.593</v>
       </c>
       <c r="G38">
         <v>395.1</v>
@@ -4403,28 +4403,28 @@
         <v>342.775</v>
       </c>
       <c r="M38">
-        <v>67.66530119999999</v>
+        <v>69.54489289999999</v>
       </c>
       <c r="N38">
-        <v>275.1096988</v>
+        <v>273.2301071</v>
       </c>
       <c r="O38">
-        <v>46.768648796</v>
+        <v>46.44911820700001</v>
       </c>
       <c r="P38">
-        <v>228.341050004</v>
+        <v>226.780988893</v>
       </c>
       <c r="Q38">
-        <v>308.441050004</v>
+        <v>306.880988893</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07275701574620437</v>
+        <v>0.07313531568786155</v>
       </c>
       <c r="T38">
-        <v>0.6225638740462902</v>
+        <v>0.6313005932531538</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.065742617281072</v>
+        <v>4.928830654651853</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06305787888335278</v>
+        <v>0.06302762768913477</v>
       </c>
       <c r="C39">
-        <v>2152.62911147643</v>
+        <v>2120.002127434346</v>
       </c>
       <c r="D39">
-        <v>3015.12211147643</v>
+        <v>3016.484127434346</v>
       </c>
       <c r="E39">
-        <v>-1843.107</v>
+        <v>-1809.118</v>
       </c>
       <c r="F39">
-        <v>1257.593</v>
+        <v>1291.582</v>
       </c>
       <c r="G39">
         <v>395.1</v>
@@ -4485,28 +4485,28 @@
         <v>342.775</v>
       </c>
       <c r="M39">
-        <v>69.54489289999999</v>
+        <v>71.4244846</v>
       </c>
       <c r="N39">
-        <v>273.2301071</v>
+        <v>271.3505153999999</v>
       </c>
       <c r="O39">
-        <v>46.44911820700001</v>
+        <v>46.129587618</v>
       </c>
       <c r="P39">
-        <v>226.780988893</v>
+        <v>225.220927782</v>
       </c>
       <c r="Q39">
-        <v>306.880988893</v>
+        <v>305.320927782</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07313531568786155</v>
+        <v>0.07352581885344317</v>
       </c>
       <c r="T39">
-        <v>0.6313005932531538</v>
+        <v>0.6403191421118517</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.928830654651853</v>
+        <v>4.799124584792593</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06302762768913477</v>
+        <v>0.06299737649491675</v>
       </c>
       <c r="C40">
-        <v>2120.002127434346</v>
+        <v>2087.376374470656</v>
       </c>
       <c r="D40">
-        <v>3016.484127434346</v>
+        <v>3017.847374470656</v>
       </c>
       <c r="E40">
-        <v>-1809.118</v>
+        <v>-1775.129</v>
       </c>
       <c r="F40">
-        <v>1291.582</v>
+        <v>1325.571</v>
       </c>
       <c r="G40">
         <v>395.1</v>
@@ -4567,28 +4567,28 @@
         <v>342.775</v>
       </c>
       <c r="M40">
-        <v>71.4244846</v>
+        <v>73.30407629999999</v>
       </c>
       <c r="N40">
-        <v>271.3505153999999</v>
+        <v>269.4709237</v>
       </c>
       <c r="O40">
-        <v>46.129587618</v>
+        <v>45.810057029</v>
       </c>
       <c r="P40">
-        <v>225.220927782</v>
+        <v>223.660866671</v>
       </c>
       <c r="Q40">
-        <v>305.320927782</v>
+        <v>303.760866671</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07352581885344317</v>
+        <v>0.07392912540150287</v>
       </c>
       <c r="T40">
-        <v>0.6403191421118517</v>
+        <v>0.6496333810970641</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.799124584792593</v>
+        <v>4.67607010825945</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06299737649491675</v>
+        <v>0.06296712530069874</v>
       </c>
       <c r="C41">
-        <v>2087.376374470656</v>
+        <v>2054.751854255207</v>
       </c>
       <c r="D41">
-        <v>3017.847374470656</v>
+        <v>3019.211854255208</v>
       </c>
       <c r="E41">
-        <v>-1775.129</v>
+        <v>-1741.14</v>
       </c>
       <c r="F41">
-        <v>1325.571</v>
+        <v>1359.56</v>
       </c>
       <c r="G41">
         <v>395.1</v>
@@ -4649,28 +4649,28 @@
         <v>342.775</v>
       </c>
       <c r="M41">
-        <v>73.30407629999999</v>
+        <v>75.183668</v>
       </c>
       <c r="N41">
-        <v>269.4709237</v>
+        <v>267.591332</v>
       </c>
       <c r="O41">
-        <v>45.810057029</v>
+        <v>45.49052644</v>
       </c>
       <c r="P41">
-        <v>223.660866671</v>
+        <v>222.10080556</v>
       </c>
       <c r="Q41">
-        <v>303.760866671</v>
+        <v>302.20080556</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07392912540150287</v>
+        <v>0.07434587550116457</v>
       </c>
       <c r="T41">
-        <v>0.6496333810970641</v>
+        <v>0.6592580947151171</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.67607010825945</v>
+        <v>4.559168355552964</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06296712530069874</v>
+        <v>0.06378762410648073</v>
       </c>
       <c r="C42">
-        <v>2054.751854255207</v>
+        <v>1984.186081424563</v>
       </c>
       <c r="D42">
-        <v>3019.211854255208</v>
+        <v>2982.635081424563</v>
       </c>
       <c r="E42">
-        <v>-1741.14</v>
+        <v>-1707.151</v>
       </c>
       <c r="F42">
-        <v>1359.56</v>
+        <v>1393.549</v>
       </c>
       <c r="G42">
         <v>395.1</v>
@@ -4731,45 +4731,45 @@
         <v>342.775</v>
       </c>
       <c r="M42">
-        <v>75.183668</v>
+        <v>80.54713220000001</v>
       </c>
       <c r="N42">
-        <v>267.591332</v>
+        <v>262.2278678</v>
       </c>
       <c r="O42">
-        <v>45.49052644</v>
+        <v>44.578737526</v>
       </c>
       <c r="P42">
-        <v>222.10080556</v>
+        <v>217.649130274</v>
       </c>
       <c r="Q42">
-        <v>302.20080556</v>
+        <v>297.749130274</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07434587550116457</v>
+        <v>0.0747767527228487</v>
       </c>
       <c r="T42">
-        <v>0.6592580947151171</v>
+        <v>0.6692090698117482</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.17</v>
       </c>
       <c r="W42">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.559168355552964</v>
+        <v>4.25558291943757</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06378762410648073</v>
+        <v>0.06377812291226272</v>
       </c>
       <c r="C43">
-        <v>1984.186081424563</v>
+        <v>1950.615559867008</v>
       </c>
       <c r="D43">
-        <v>2982.635081424563</v>
+        <v>2983.053559867008</v>
       </c>
       <c r="E43">
-        <v>-1707.151</v>
+        <v>-1673.162</v>
       </c>
       <c r="F43">
-        <v>1393.549</v>
+        <v>1427.538</v>
       </c>
       <c r="G43">
         <v>395.1</v>
@@ -4813,28 +4813,28 @@
         <v>342.775</v>
       </c>
       <c r="M43">
-        <v>80.54713220000001</v>
+        <v>82.51169640000001</v>
       </c>
       <c r="N43">
-        <v>262.2278678</v>
+        <v>260.2633036</v>
       </c>
       <c r="O43">
-        <v>44.578737526</v>
+        <v>44.244761612</v>
       </c>
       <c r="P43">
-        <v>217.649130274</v>
+        <v>216.018541988</v>
       </c>
       <c r="Q43">
-        <v>297.749130274</v>
+        <v>296.118541988</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0747767527228487</v>
+        <v>0.07522248777976331</v>
       </c>
       <c r="T43">
-        <v>0.6692090698117482</v>
+        <v>0.6795031819806768</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.25558291943757</v>
+        <v>4.154259516593819</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06377812291226272</v>
+        <v>0.06376862171804472</v>
       </c>
       <c r="C44">
-        <v>1950.615559867008</v>
+        <v>1917.045155755118</v>
       </c>
       <c r="D44">
-        <v>2983.053559867008</v>
+        <v>2983.472155755118</v>
       </c>
       <c r="E44">
-        <v>-1673.162</v>
+        <v>-1639.173</v>
       </c>
       <c r="F44">
-        <v>1427.538</v>
+        <v>1461.527</v>
       </c>
       <c r="G44">
         <v>395.1</v>
@@ -4895,28 +4895,28 @@
         <v>342.775</v>
       </c>
       <c r="M44">
-        <v>82.51169639999999</v>
+        <v>84.47626059999999</v>
       </c>
       <c r="N44">
-        <v>260.2633036</v>
+        <v>258.2987394</v>
       </c>
       <c r="O44">
-        <v>44.244761612</v>
+        <v>43.910785698</v>
       </c>
       <c r="P44">
-        <v>216.018541988</v>
+        <v>214.387953702</v>
       </c>
       <c r="Q44">
-        <v>296.118541988</v>
+        <v>294.487953702</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0752224877797633</v>
+        <v>0.07568386266323633</v>
       </c>
       <c r="T44">
-        <v>0.6795031819806767</v>
+        <v>0.6901584910678136</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.15425951659382</v>
+        <v>4.057648830161405</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06376862171804472</v>
+        <v>0.0650373205238267</v>
       </c>
       <c r="C45">
-        <v>1917.045155755118</v>
+        <v>1828.181236976171</v>
       </c>
       <c r="D45">
-        <v>2983.472155755118</v>
+        <v>2928.597236976171</v>
       </c>
       <c r="E45">
-        <v>-1639.173</v>
+        <v>-1605.184</v>
       </c>
       <c r="F45">
-        <v>1461.527</v>
+        <v>1495.516</v>
       </c>
       <c r="G45">
         <v>395.1</v>
@@ -4977,45 +4977,45 @@
         <v>342.775</v>
       </c>
       <c r="M45">
-        <v>84.47626059999999</v>
+        <v>91.67513079999999</v>
       </c>
       <c r="N45">
-        <v>258.2987394</v>
+        <v>251.0998692</v>
       </c>
       <c r="O45">
-        <v>43.910785698</v>
+        <v>42.68697776400001</v>
       </c>
       <c r="P45">
-        <v>214.387953702</v>
+        <v>208.412891436</v>
       </c>
       <c r="Q45">
-        <v>294.487953702</v>
+        <v>288.512891436</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07568386266323633</v>
+        <v>0.0761617152211191</v>
       </c>
       <c r="T45">
-        <v>0.6901584910678136</v>
+        <v>0.7011943469080623</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.17</v>
       </c>
       <c r="W45">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.057648830161405</v>
+        <v>3.739018390361544</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0650373205238267</v>
+        <v>0.06505686932960869</v>
       </c>
       <c r="C46">
-        <v>1828.181236976171</v>
+        <v>1793.362481389679</v>
       </c>
       <c r="D46">
-        <v>2928.597236976171</v>
+        <v>2927.767481389679</v>
       </c>
       <c r="E46">
-        <v>-1605.184</v>
+        <v>-1571.195</v>
       </c>
       <c r="F46">
-        <v>1495.516</v>
+        <v>1529.505</v>
       </c>
       <c r="G46">
         <v>395.1</v>
@@ -5059,28 +5059,28 @@
         <v>342.775</v>
       </c>
       <c r="M46">
-        <v>91.67513079999999</v>
+        <v>93.75865649999999</v>
       </c>
       <c r="N46">
-        <v>251.0998692</v>
+        <v>249.0163435</v>
       </c>
       <c r="O46">
-        <v>42.68697776400001</v>
+        <v>42.33277839500001</v>
       </c>
       <c r="P46">
-        <v>208.412891436</v>
+        <v>206.683565105</v>
       </c>
       <c r="Q46">
-        <v>288.512891436</v>
+        <v>286.783565105</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0761617152211191</v>
+        <v>0.07665694423565214</v>
       </c>
       <c r="T46">
-        <v>0.7011943469080623</v>
+        <v>0.7126315065970472</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.739018390361544</v>
+        <v>3.655929092797955</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06505686932960869</v>
+        <v>0.06507641813539067</v>
       </c>
       <c r="C47">
-        <v>1793.362481389679</v>
+        <v>1758.544195857117</v>
       </c>
       <c r="D47">
-        <v>2927.767481389679</v>
+        <v>2926.938195857117</v>
       </c>
       <c r="E47">
-        <v>-1571.195</v>
+        <v>-1537.206</v>
       </c>
       <c r="F47">
-        <v>1529.505</v>
+        <v>1563.494</v>
       </c>
       <c r="G47">
         <v>395.1</v>
@@ -5141,28 +5141,28 @@
         <v>342.775</v>
       </c>
       <c r="M47">
-        <v>93.75865649999999</v>
+        <v>95.8421822</v>
       </c>
       <c r="N47">
-        <v>249.0163435</v>
+        <v>246.9328178</v>
       </c>
       <c r="O47">
-        <v>42.33277839500001</v>
+        <v>41.978579026</v>
       </c>
       <c r="P47">
-        <v>206.683565105</v>
+        <v>204.954238774</v>
       </c>
       <c r="Q47">
-        <v>286.783565105</v>
+        <v>285.054238774</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07665694423565214</v>
+        <v>0.07717051506553826</v>
       </c>
       <c r="T47">
-        <v>0.7126315065970472</v>
+        <v>0.7244922647930317</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.655929092797955</v>
+        <v>3.576452373389303</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06507641813539067</v>
+        <v>0.06509596694117266</v>
       </c>
       <c r="C48">
-        <v>1758.544195857117</v>
+        <v>1723.726379979169</v>
       </c>
       <c r="D48">
-        <v>2926.938195857117</v>
+        <v>2926.109379979169</v>
       </c>
       <c r="E48">
-        <v>-1537.206</v>
+        <v>-1503.217</v>
       </c>
       <c r="F48">
-        <v>1563.494</v>
+        <v>1597.483</v>
       </c>
       <c r="G48">
         <v>395.1</v>
@@ -5223,28 +5223,28 @@
         <v>342.775</v>
       </c>
       <c r="M48">
-        <v>95.8421822</v>
+        <v>97.92570789999999</v>
       </c>
       <c r="N48">
-        <v>246.9328178</v>
+        <v>244.8492921</v>
       </c>
       <c r="O48">
-        <v>41.978579026</v>
+        <v>41.624379657</v>
       </c>
       <c r="P48">
-        <v>204.954238774</v>
+        <v>203.224912443</v>
       </c>
       <c r="Q48">
-        <v>285.054238774</v>
+        <v>283.324912443</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07717051506553826</v>
+        <v>0.07770346592674085</v>
       </c>
       <c r="T48">
-        <v>0.7244922647930317</v>
+        <v>0.7368005987699967</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.576452373389303</v>
+        <v>3.500357642040594</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06509596694117266</v>
+        <v>0.06623103574695464</v>
       </c>
       <c r="C49">
-        <v>1723.726379979169</v>
+        <v>1642.405412943048</v>
       </c>
       <c r="D49">
-        <v>2926.109379979169</v>
+        <v>2878.777412943048</v>
       </c>
       <c r="E49">
-        <v>-1503.217</v>
+        <v>-1469.228</v>
       </c>
       <c r="F49">
-        <v>1597.483</v>
+        <v>1631.472</v>
       </c>
       <c r="G49">
         <v>395.1</v>
@@ -5305,45 +5305,45 @@
         <v>342.775</v>
       </c>
       <c r="M49">
-        <v>97.92570789999999</v>
+        <v>104.5773552</v>
       </c>
       <c r="N49">
-        <v>244.8492921</v>
+        <v>238.1976448</v>
       </c>
       <c r="O49">
-        <v>41.624379657</v>
+        <v>40.493599616</v>
       </c>
       <c r="P49">
-        <v>203.224912443</v>
+        <v>197.704045184</v>
       </c>
       <c r="Q49">
-        <v>283.324912443</v>
+        <v>277.804045184</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.07770346592674085</v>
+        <v>0.07825691489798969</v>
       </c>
       <c r="T49">
-        <v>0.7368005987699967</v>
+        <v>0.7495823302076142</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.17</v>
       </c>
       <c r="W49">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.500357642040594</v>
+        <v>3.277717239496606</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06623103574695464</v>
+        <v>0.06627382455273663</v>
       </c>
       <c r="C50">
-        <v>1642.405412943048</v>
+        <v>1606.662066671702</v>
       </c>
       <c r="D50">
-        <v>2878.777412943048</v>
+        <v>2877.023066671702</v>
       </c>
       <c r="E50">
-        <v>-1469.228</v>
+        <v>-1435.239</v>
       </c>
       <c r="F50">
-        <v>1631.472</v>
+        <v>1665.461</v>
       </c>
       <c r="G50">
         <v>395.1</v>
@@ -5387,28 +5387,28 @@
         <v>342.775</v>
       </c>
       <c r="M50">
-        <v>104.5773552</v>
+        <v>106.7560501</v>
       </c>
       <c r="N50">
-        <v>238.1976448</v>
+        <v>236.0189499</v>
       </c>
       <c r="O50">
-        <v>40.493599616</v>
+        <v>40.123221483</v>
       </c>
       <c r="P50">
-        <v>197.704045184</v>
+        <v>195.895728417</v>
       </c>
       <c r="Q50">
-        <v>277.804045184</v>
+        <v>275.995728417</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.07825691489798969</v>
+        <v>0.07883206775046397</v>
       </c>
       <c r="T50">
-        <v>0.7495823302076142</v>
+        <v>0.7628653060153343</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.277717239496606</v>
+        <v>3.21082505093545</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06627382455273663</v>
+        <v>0.06631661335851861</v>
       </c>
       <c r="C51">
-        <v>1606.662066671702</v>
+        <v>1570.920857318882</v>
       </c>
       <c r="D51">
-        <v>2877.023066671702</v>
+        <v>2875.270857318882</v>
       </c>
       <c r="E51">
-        <v>-1435.239</v>
+        <v>-1401.25</v>
       </c>
       <c r="F51">
-        <v>1665.461</v>
+        <v>1699.45</v>
       </c>
       <c r="G51">
         <v>395.1</v>
@@ -5469,28 +5469,28 @@
         <v>342.775</v>
       </c>
       <c r="M51">
-        <v>106.7560501</v>
+        <v>108.934745</v>
       </c>
       <c r="N51">
-        <v>236.0189499</v>
+        <v>233.840255</v>
       </c>
       <c r="O51">
-        <v>40.123221483</v>
+        <v>39.75284335</v>
       </c>
       <c r="P51">
-        <v>195.895728417</v>
+        <v>194.08741165</v>
       </c>
       <c r="Q51">
-        <v>275.995728417</v>
+        <v>274.18741165</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.07883206775046397</v>
+        <v>0.07943022671703723</v>
       </c>
       <c r="T51">
-        <v>0.7628653060153343</v>
+        <v>0.7766796008553634</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.21082505093545</v>
+        <v>3.146608549916742</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06631661335851861</v>
+        <v>0.0663594021643006</v>
       </c>
       <c r="C52">
-        <v>1570.920857318882</v>
+        <v>1535.181780982585</v>
       </c>
       <c r="D52">
-        <v>2875.270857318882</v>
+        <v>2873.520780982585</v>
       </c>
       <c r="E52">
-        <v>-1401.25</v>
+        <v>-1367.261</v>
       </c>
       <c r="F52">
-        <v>1699.45</v>
+        <v>1733.439</v>
       </c>
       <c r="G52">
         <v>395.1</v>
@@ -5551,28 +5551,28 @@
         <v>342.775</v>
       </c>
       <c r="M52">
-        <v>108.934745</v>
+        <v>111.1134399</v>
       </c>
       <c r="N52">
-        <v>233.840255</v>
+        <v>231.6615601</v>
       </c>
       <c r="O52">
-        <v>39.75284335</v>
+        <v>39.382465217</v>
       </c>
       <c r="P52">
-        <v>194.08741165</v>
+        <v>192.279094883</v>
       </c>
       <c r="Q52">
-        <v>274.18741165</v>
+        <v>272.379094883</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.07943022671703723</v>
+        <v>0.08005280033530734</v>
       </c>
       <c r="T52">
-        <v>0.7766796008553634</v>
+        <v>0.791057744464373</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.146608549916742</v>
+        <v>3.084910343055629</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0663594021643006</v>
+        <v>0.0664021909700826</v>
       </c>
       <c r="C53">
-        <v>1535.181780982585</v>
+        <v>1499.444833770305</v>
       </c>
       <c r="D53">
-        <v>2873.520780982585</v>
+        <v>2871.772833770305</v>
       </c>
       <c r="E53">
-        <v>-1367.261</v>
+        <v>-1333.272</v>
       </c>
       <c r="F53">
-        <v>1733.439</v>
+        <v>1767.428</v>
       </c>
       <c r="G53">
         <v>395.1</v>
@@ -5633,28 +5633,28 @@
         <v>342.775</v>
       </c>
       <c r="M53">
-        <v>111.1134399</v>
+        <v>113.2921348</v>
       </c>
       <c r="N53">
-        <v>231.6615601</v>
+        <v>229.4828652</v>
       </c>
       <c r="O53">
-        <v>39.382465217</v>
+        <v>39.012087084</v>
       </c>
       <c r="P53">
-        <v>192.279094883</v>
+        <v>190.470778116</v>
       </c>
       <c r="Q53">
-        <v>272.379094883</v>
+        <v>270.570778116</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08005280033530734</v>
+        <v>0.0807013145210054</v>
       </c>
       <c r="T53">
-        <v>0.791057744464373</v>
+        <v>0.806034977390425</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.084910343055629</v>
+        <v>3.025585144150713</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0664021909700826</v>
+        <v>0.06987619977586457</v>
       </c>
       <c r="C54">
-        <v>1499.444833770305</v>
+        <v>1330.301795853704</v>
       </c>
       <c r="D54">
-        <v>2871.772833770305</v>
+        <v>2736.618795853704</v>
       </c>
       <c r="E54">
-        <v>-1333.272</v>
+        <v>-1299.283</v>
       </c>
       <c r="F54">
-        <v>1767.428</v>
+        <v>1801.417</v>
       </c>
       <c r="G54">
         <v>395.1</v>
@@ -5715,45 +5715,45 @@
         <v>342.775</v>
       </c>
       <c r="M54">
-        <v>113.2921348</v>
+        <v>129.5218823</v>
       </c>
       <c r="N54">
-        <v>229.4828652</v>
+        <v>213.2531177</v>
       </c>
       <c r="O54">
-        <v>39.012087084</v>
+        <v>36.25303000899999</v>
       </c>
       <c r="P54">
-        <v>190.470778116</v>
+        <v>177.000087691</v>
       </c>
       <c r="Q54">
-        <v>270.570778116</v>
+        <v>257.100087691</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0807013145210054</v>
+        <v>0.08137742505503101</v>
       </c>
       <c r="T54">
-        <v>0.806034977390425</v>
+        <v>0.8216495393771598</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.17</v>
       </c>
       <c r="W54">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.025585144150713</v>
+        <v>2.646464009888775</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06987619977586457</v>
+        <v>0.06998372858164656</v>
       </c>
       <c r="C55">
-        <v>1330.301795853704</v>
+        <v>1292.33213685824</v>
       </c>
       <c r="D55">
-        <v>2736.618795853704</v>
+        <v>2732.63813685824</v>
       </c>
       <c r="E55">
-        <v>-1299.283</v>
+        <v>-1265.294</v>
       </c>
       <c r="F55">
-        <v>1801.417</v>
+        <v>1835.406</v>
       </c>
       <c r="G55">
         <v>395.1</v>
@@ -5797,28 +5797,28 @@
         <v>342.775</v>
       </c>
       <c r="M55">
-        <v>129.5218823</v>
+        <v>131.9656914</v>
       </c>
       <c r="N55">
-        <v>213.2531177</v>
+        <v>210.8093086</v>
       </c>
       <c r="O55">
-        <v>36.25303000899999</v>
+        <v>35.837582462</v>
       </c>
       <c r="P55">
-        <v>177.000087691</v>
+        <v>174.971726138</v>
       </c>
       <c r="Q55">
-        <v>257.100087691</v>
+        <v>255.071726138</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08137742505503101</v>
+        <v>0.08208293169923167</v>
       </c>
       <c r="T55">
-        <v>0.8216495393771598</v>
+        <v>0.8379429953633178</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.646464009888775</v>
+        <v>2.597455417113057</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06998372858164656</v>
+        <v>0.07009125738742855</v>
       </c>
       <c r="C56">
-        <v>1292.33213685824</v>
+        <v>1254.374041497884</v>
       </c>
       <c r="D56">
-        <v>2732.63813685824</v>
+        <v>2728.669041497884</v>
       </c>
       <c r="E56">
-        <v>-1265.294</v>
+        <v>-1231.305</v>
       </c>
       <c r="F56">
-        <v>1835.406</v>
+        <v>1869.395</v>
       </c>
       <c r="G56">
         <v>395.1</v>
@@ -5879,28 +5879,28 @@
         <v>342.775</v>
       </c>
       <c r="M56">
-        <v>131.9656914</v>
+        <v>134.4095005</v>
       </c>
       <c r="N56">
-        <v>210.8093086</v>
+        <v>208.3654995</v>
       </c>
       <c r="O56">
-        <v>35.837582462</v>
+        <v>35.422134915</v>
       </c>
       <c r="P56">
-        <v>174.971726138</v>
+        <v>172.943364585</v>
       </c>
       <c r="Q56">
-        <v>255.071726138</v>
+        <v>253.043364585</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08208293169923167</v>
+        <v>0.08281979419428567</v>
       </c>
       <c r="T56">
-        <v>0.8379429953633178</v>
+        <v>0.8549606049488611</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.597455417113057</v>
+        <v>2.550228954983729</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07009125738742855</v>
+        <v>0.07019878619321054</v>
       </c>
       <c r="C57">
-        <v>1254.374041497884</v>
+        <v>1216.42745945796</v>
       </c>
       <c r="D57">
-        <v>2728.669041497884</v>
+        <v>2724.71145945796</v>
       </c>
       <c r="E57">
-        <v>-1231.305</v>
+        <v>-1197.316</v>
       </c>
       <c r="F57">
-        <v>1869.395</v>
+        <v>1903.384</v>
       </c>
       <c r="G57">
         <v>395.1</v>
@@ -5961,28 +5961,28 @@
         <v>342.775</v>
       </c>
       <c r="M57">
-        <v>134.4095005</v>
+        <v>136.8533096</v>
       </c>
       <c r="N57">
-        <v>208.3654995</v>
+        <v>205.9216904</v>
       </c>
       <c r="O57">
-        <v>35.422134915</v>
+        <v>35.00668736799999</v>
       </c>
       <c r="P57">
-        <v>172.943364585</v>
+        <v>170.915003032</v>
       </c>
       <c r="Q57">
-        <v>253.043364585</v>
+        <v>251.015003032</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08281979419428567</v>
+        <v>0.08359015043911486</v>
       </c>
       <c r="T57">
-        <v>0.8549606049488611</v>
+        <v>0.8727517422428376</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.550228954983729</v>
+        <v>2.504689152216162</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07019878619321054</v>
+        <v>0.07215140499899253</v>
       </c>
       <c r="C58">
-        <v>1216.42745945796</v>
+        <v>1112.518349608719</v>
       </c>
       <c r="D58">
-        <v>2724.71145945796</v>
+        <v>2654.791349608719</v>
       </c>
       <c r="E58">
-        <v>-1197.316</v>
+        <v>-1163.327</v>
       </c>
       <c r="F58">
-        <v>1903.384</v>
+        <v>1937.373</v>
       </c>
       <c r="G58">
         <v>395.1</v>
@@ -6043,45 +6043,45 @@
         <v>342.775</v>
       </c>
       <c r="M58">
-        <v>136.8533096</v>
+        <v>146.8528734</v>
       </c>
       <c r="N58">
-        <v>205.9216904</v>
+        <v>195.9221266</v>
       </c>
       <c r="O58">
-        <v>35.00668736799999</v>
+        <v>33.306761522</v>
       </c>
       <c r="P58">
-        <v>170.915003032</v>
+        <v>162.615365078</v>
       </c>
       <c r="Q58">
-        <v>251.015003032</v>
+        <v>242.715365078</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08359015043911486</v>
+        <v>0.08439633720695937</v>
       </c>
       <c r="T58">
-        <v>0.8727517422428376</v>
+        <v>0.8913703742946737</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.17</v>
       </c>
       <c r="W58">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.504689152216162</v>
+        <v>2.334138870176169</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07215140499899253</v>
+        <v>0.0722913038047745</v>
       </c>
       <c r="C59">
-        <v>1112.518349608719</v>
+        <v>1073.657310417767</v>
       </c>
       <c r="D59">
-        <v>2654.791349608719</v>
+        <v>2649.919310417768</v>
       </c>
       <c r="E59">
-        <v>-1163.327</v>
+        <v>-1129.338</v>
       </c>
       <c r="F59">
-        <v>1937.373</v>
+        <v>1971.362</v>
       </c>
       <c r="G59">
         <v>395.1</v>
@@ -6125,28 +6125,28 @@
         <v>342.775</v>
       </c>
       <c r="M59">
-        <v>146.8528734</v>
+        <v>149.4292396</v>
       </c>
       <c r="N59">
-        <v>195.9221266</v>
+        <v>193.3457604</v>
       </c>
       <c r="O59">
-        <v>33.306761522</v>
+        <v>32.868779268</v>
       </c>
       <c r="P59">
-        <v>162.615365078</v>
+        <v>160.476981132</v>
       </c>
       <c r="Q59">
-        <v>242.715365078</v>
+        <v>240.576981132</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08439633720695937</v>
+        <v>0.08524091382089169</v>
       </c>
       <c r="T59">
-        <v>0.8913703742946737</v>
+        <v>0.9108756078727875</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.334138870176169</v>
+        <v>2.293895096552442</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0722913038047745</v>
+        <v>0.07243120261055649</v>
       </c>
       <c r="C60">
-        <v>1073.657310417768</v>
+        <v>1034.814120677973</v>
       </c>
       <c r="D60">
-        <v>2649.919310417768</v>
+        <v>2645.065120677973</v>
       </c>
       <c r="E60">
-        <v>-1129.338</v>
+        <v>-1095.349</v>
       </c>
       <c r="F60">
-        <v>1971.362</v>
+        <v>2005.351</v>
       </c>
       <c r="G60">
         <v>395.1</v>
@@ -6207,28 +6207,28 @@
         <v>342.775</v>
       </c>
       <c r="M60">
-        <v>149.4292396</v>
+        <v>152.0056058</v>
       </c>
       <c r="N60">
-        <v>193.3457604</v>
+        <v>190.7693942</v>
       </c>
       <c r="O60">
-        <v>32.868779268</v>
+        <v>32.430797014</v>
       </c>
       <c r="P60">
-        <v>160.476981132</v>
+        <v>158.338597186</v>
       </c>
       <c r="Q60">
-        <v>240.576981132</v>
+        <v>238.438597186</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.08524091382089169</v>
+        <v>0.08612668929404024</v>
       </c>
       <c r="T60">
-        <v>0.9108756078727875</v>
+        <v>0.93133231625959</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.293895096552442</v>
+        <v>2.255015518644774</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07243120261055649</v>
+        <v>0.07257110141633849</v>
       </c>
       <c r="C61">
-        <v>1034.814120677973</v>
+        <v>995.9886824774558</v>
       </c>
       <c r="D61">
-        <v>2645.065120677973</v>
+        <v>2640.228682477456</v>
       </c>
       <c r="E61">
-        <v>-1095.349</v>
+        <v>-1061.36</v>
       </c>
       <c r="F61">
-        <v>2005.351</v>
+        <v>2039.34</v>
       </c>
       <c r="G61">
         <v>395.1</v>
@@ -6289,28 +6289,28 @@
         <v>342.775</v>
       </c>
       <c r="M61">
-        <v>152.0056058</v>
+        <v>154.581972</v>
       </c>
       <c r="N61">
-        <v>190.7693942</v>
+        <v>188.193028</v>
       </c>
       <c r="O61">
-        <v>32.430797014</v>
+        <v>31.99281476</v>
       </c>
       <c r="P61">
-        <v>158.338597186</v>
+        <v>156.20021324</v>
       </c>
       <c r="Q61">
-        <v>238.438597186</v>
+        <v>236.30021324</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08612668929404024</v>
+        <v>0.08705675354084622</v>
       </c>
       <c r="T61">
-        <v>0.93133231625959</v>
+        <v>0.9528118600657325</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.255015518644774</v>
+        <v>2.217431926667361</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07257110141633849</v>
+        <v>0.07271100022212047</v>
       </c>
       <c r="C62">
-        <v>995.9886824774558</v>
+        <v>957.1808986191459</v>
       </c>
       <c r="D62">
-        <v>2640.228682477456</v>
+        <v>2635.409898619146</v>
       </c>
       <c r="E62">
-        <v>-1061.36</v>
+        <v>-1027.371</v>
       </c>
       <c r="F62">
-        <v>2039.34</v>
+        <v>2073.329</v>
       </c>
       <c r="G62">
         <v>395.1</v>
@@ -6371,28 +6371,28 @@
         <v>342.775</v>
       </c>
       <c r="M62">
-        <v>154.581972</v>
+        <v>157.1583382</v>
       </c>
       <c r="N62">
-        <v>188.193028</v>
+        <v>185.6166618</v>
       </c>
       <c r="O62">
-        <v>31.99281476</v>
+        <v>31.554832506</v>
       </c>
       <c r="P62">
-        <v>156.20021324</v>
+        <v>154.061829294</v>
       </c>
       <c r="Q62">
-        <v>236.30021324</v>
+        <v>234.161829294</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.08705675354084622</v>
+        <v>0.0880345133900525</v>
       </c>
       <c r="T62">
-        <v>0.9528118600657325</v>
+        <v>0.9753929189388568</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.217431926667361</v>
+        <v>2.18108058360724</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07271100022212047</v>
+        <v>0.07285089902790245</v>
       </c>
       <c r="C63">
-        <v>957.1808986191459</v>
+        <v>918.3906726142723</v>
       </c>
       <c r="D63">
-        <v>2635.409898619146</v>
+        <v>2630.608672614272</v>
       </c>
       <c r="E63">
-        <v>-1027.371</v>
+        <v>-993.3820000000001</v>
       </c>
       <c r="F63">
-        <v>2073.329</v>
+        <v>2107.318</v>
       </c>
       <c r="G63">
         <v>395.1</v>
@@ -6453,28 +6453,28 @@
         <v>342.775</v>
       </c>
       <c r="M63">
-        <v>157.1583382</v>
+        <v>159.7347044</v>
       </c>
       <c r="N63">
-        <v>185.6166618</v>
+        <v>183.0402956</v>
       </c>
       <c r="O63">
-        <v>31.554832506</v>
+        <v>31.116850252</v>
       </c>
       <c r="P63">
-        <v>154.061829294</v>
+        <v>151.923445348</v>
       </c>
       <c r="Q63">
-        <v>234.161829294</v>
+        <v>232.023445348</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.0880345133900525</v>
+        <v>0.08906373428395385</v>
       </c>
       <c r="T63">
-        <v>0.9753929189388568</v>
+        <v>0.9991624545947771</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.18108058360724</v>
+        <v>2.145901864516801</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07285089902790245</v>
+        <v>0.07299079783368445</v>
       </c>
       <c r="C64">
-        <v>918.3906726142723</v>
+        <v>879.6179086759239</v>
       </c>
       <c r="D64">
-        <v>2630.608672614272</v>
+        <v>2625.824908675924</v>
       </c>
       <c r="E64">
-        <v>-993.3820000000001</v>
+        <v>-959.393</v>
       </c>
       <c r="F64">
-        <v>2107.318</v>
+        <v>2141.307</v>
       </c>
       <c r="G64">
         <v>395.1</v>
@@ -6535,28 +6535,28 @@
         <v>342.775</v>
       </c>
       <c r="M64">
-        <v>159.7347044</v>
+        <v>162.3110706</v>
       </c>
       <c r="N64">
-        <v>183.0402956</v>
+        <v>180.4639294</v>
       </c>
       <c r="O64">
-        <v>31.116850252</v>
+        <v>30.678867998</v>
       </c>
       <c r="P64">
-        <v>151.923445348</v>
+        <v>149.785061402</v>
       </c>
       <c r="Q64">
-        <v>232.023445348</v>
+        <v>229.885061402</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.08906373428395385</v>
+        <v>0.0901485887396877</v>
       </c>
       <c r="T64">
-        <v>0.9991624545947771</v>
+        <v>1.024216830015882</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.145901864516801</v>
+        <v>2.111839930159391</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07299079783368445</v>
+        <v>0.07313069663946643</v>
       </c>
       <c r="C65">
-        <v>879.6179086759239</v>
+        <v>840.8625117126799</v>
       </c>
       <c r="D65">
-        <v>2625.824908675924</v>
+        <v>2621.05851171268</v>
       </c>
       <c r="E65">
-        <v>-959.393</v>
+        <v>-925.404</v>
       </c>
       <c r="F65">
-        <v>2141.307</v>
+        <v>2175.296</v>
       </c>
       <c r="G65">
         <v>395.1</v>
@@ -6617,28 +6617,28 @@
         <v>342.775</v>
       </c>
       <c r="M65">
-        <v>162.3110706</v>
+        <v>164.8874368</v>
       </c>
       <c r="N65">
-        <v>180.4639294</v>
+        <v>177.8875632</v>
       </c>
       <c r="O65">
-        <v>30.678867998</v>
+        <v>30.240885744</v>
       </c>
       <c r="P65">
-        <v>149.785061402</v>
+        <v>147.646677456</v>
       </c>
       <c r="Q65">
-        <v>229.885061402</v>
+        <v>227.746677456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.0901485887396877</v>
+        <v>0.09129371288740676</v>
       </c>
       <c r="T65">
-        <v>1.024216830015882</v>
+        <v>1.050663115182604</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.111839930159391</v>
+        <v>2.078842431250651</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07313069663946643</v>
+        <v>0.07327059544524843</v>
       </c>
       <c r="C66">
-        <v>840.8625117126799</v>
+        <v>802.1243873223075</v>
       </c>
       <c r="D66">
-        <v>2621.05851171268</v>
+        <v>2616.309387322307</v>
       </c>
       <c r="E66">
-        <v>-925.404</v>
+        <v>-891.415</v>
       </c>
       <c r="F66">
-        <v>2175.296</v>
+        <v>2209.285</v>
       </c>
       <c r="G66">
         <v>395.1</v>
@@ -6699,28 +6699,28 @@
         <v>342.775</v>
       </c>
       <c r="M66">
-        <v>164.8874368</v>
+        <v>167.463803</v>
       </c>
       <c r="N66">
-        <v>177.8875632</v>
+        <v>175.311197</v>
       </c>
       <c r="O66">
-        <v>30.240885744</v>
+        <v>29.80290348999999</v>
       </c>
       <c r="P66">
-        <v>147.646677456</v>
+        <v>145.50829351</v>
       </c>
       <c r="Q66">
-        <v>227.746677456</v>
+        <v>225.60829351</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09129371288740676</v>
+        <v>0.09250427270070979</v>
       </c>
       <c r="T66">
-        <v>1.050663115182604</v>
+        <v>1.078620616644568</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.078842431250651</v>
+        <v>2.04686024000064</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07327059544524843</v>
+        <v>0.07341049425103041</v>
       </c>
       <c r="C67">
-        <v>802.1243873223075</v>
+        <v>763.403441785531</v>
       </c>
       <c r="D67">
-        <v>2616.309387322307</v>
+        <v>2611.577441785531</v>
       </c>
       <c r="E67">
-        <v>-891.415</v>
+        <v>-857.4259999999999</v>
       </c>
       <c r="F67">
-        <v>2209.285</v>
+        <v>2243.274</v>
       </c>
       <c r="G67">
         <v>395.1</v>
@@ -6781,28 +6781,28 @@
         <v>342.775</v>
       </c>
       <c r="M67">
-        <v>167.463803</v>
+        <v>170.0401692</v>
       </c>
       <c r="N67">
-        <v>175.311197</v>
+        <v>172.7348308</v>
       </c>
       <c r="O67">
-        <v>29.80290348999999</v>
+        <v>29.364921236</v>
       </c>
       <c r="P67">
-        <v>145.50829351</v>
+        <v>143.369909564</v>
       </c>
       <c r="Q67">
-        <v>225.60829351</v>
+        <v>223.469909564</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09250427270070979</v>
+        <v>0.09378604191479534</v>
       </c>
       <c r="T67">
-        <v>1.078620616644568</v>
+        <v>1.108222677016059</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.04686024000064</v>
+        <v>2.015847206061236</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07341049425103041</v>
+        <v>0.0814470130568124</v>
       </c>
       <c r="C68">
-        <v>763.403441785531</v>
+        <v>483.6161830171859</v>
       </c>
       <c r="D68">
-        <v>2611.577441785531</v>
+        <v>2365.779183017186</v>
       </c>
       <c r="E68">
-        <v>-857.4259999999999</v>
+        <v>-823.4369999999999</v>
       </c>
       <c r="F68">
-        <v>2243.274</v>
+        <v>2277.263</v>
       </c>
       <c r="G68">
         <v>395.1</v>
@@ -6863,45 +6863,45 @@
         <v>342.775</v>
       </c>
       <c r="M68">
-        <v>170.0401692</v>
+        <v>204.95367</v>
       </c>
       <c r="N68">
-        <v>172.7348308</v>
+        <v>137.82133</v>
       </c>
       <c r="O68">
-        <v>29.364921236</v>
+        <v>23.4296261</v>
       </c>
       <c r="P68">
-        <v>143.369909564</v>
+        <v>114.3917039</v>
       </c>
       <c r="Q68">
-        <v>223.469909564</v>
+        <v>194.4917039</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09378604191479534</v>
+        <v>0.09514549411155274</v>
       </c>
       <c r="T68">
-        <v>1.108222677016059</v>
+        <v>1.139618801652488</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.17</v>
       </c>
       <c r="W68">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.015847206061236</v>
+        <v>1.672451144690407</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0814470130568124</v>
+        <v>0.08170477186259438</v>
       </c>
       <c r="C69">
-        <v>483.6161830171859</v>
+        <v>442.5070745342177</v>
       </c>
       <c r="D69">
-        <v>2365.779183017186</v>
+        <v>2358.659074534218</v>
       </c>
       <c r="E69">
-        <v>-823.4369999999999</v>
+        <v>-789.4479999999999</v>
       </c>
       <c r="F69">
-        <v>2277.263</v>
+        <v>2311.252</v>
       </c>
       <c r="G69">
         <v>395.1</v>
@@ -6945,28 +6945,28 @@
         <v>342.775</v>
       </c>
       <c r="M69">
-        <v>204.95367</v>
+        <v>208.01268</v>
       </c>
       <c r="N69">
-        <v>137.82133</v>
+        <v>134.76232</v>
       </c>
       <c r="O69">
-        <v>23.4296261</v>
+        <v>22.9095944</v>
       </c>
       <c r="P69">
-        <v>114.3917039</v>
+        <v>111.8527256</v>
       </c>
       <c r="Q69">
-        <v>194.4917039</v>
+        <v>191.9527256</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09514549411155274</v>
+        <v>0.09658991207060746</v>
       </c>
       <c r="T69">
-        <v>1.139618801652488</v>
+        <v>1.172977184078694</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.672451144690407</v>
+        <v>1.647856274915549</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08170477186259438</v>
+        <v>0.08196253066837637</v>
       </c>
       <c r="C70">
-        <v>442.5070745342177</v>
+        <v>401.440695167475</v>
       </c>
       <c r="D70">
-        <v>2358.659074534218</v>
+        <v>2351.581695167475</v>
       </c>
       <c r="E70">
-        <v>-789.4479999999999</v>
+        <v>-755.4589999999998</v>
       </c>
       <c r="F70">
-        <v>2311.252</v>
+        <v>2345.241</v>
       </c>
       <c r="G70">
         <v>395.1</v>
@@ -7027,28 +7027,28 @@
         <v>342.775</v>
       </c>
       <c r="M70">
-        <v>208.01268</v>
+        <v>211.07169</v>
       </c>
       <c r="N70">
-        <v>134.76232</v>
+        <v>131.70331</v>
       </c>
       <c r="O70">
-        <v>22.9095944</v>
+        <v>22.3895627</v>
       </c>
       <c r="P70">
-        <v>111.8527256</v>
+        <v>109.3137473</v>
       </c>
       <c r="Q70">
-        <v>191.9527256</v>
+        <v>189.4137473</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.09658991207060746</v>
+        <v>0.09812751828508509</v>
       </c>
       <c r="T70">
-        <v>1.172977184078694</v>
+        <v>1.208487720209817</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.647856274915549</v>
+        <v>1.623974299916772</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08196253066837637</v>
+        <v>0.08222028947415835</v>
       </c>
       <c r="C71">
-        <v>401.440695167475</v>
+        <v>360.4166614294004</v>
       </c>
       <c r="D71">
-        <v>2351.581695167475</v>
+        <v>2344.546661429401</v>
       </c>
       <c r="E71">
-        <v>-755.4589999999998</v>
+        <v>-721.4699999999998</v>
       </c>
       <c r="F71">
-        <v>2345.241</v>
+        <v>2379.23</v>
       </c>
       <c r="G71">
         <v>395.1</v>
@@ -7109,28 +7109,28 @@
         <v>342.775</v>
       </c>
       <c r="M71">
-        <v>211.07169</v>
+        <v>214.1307</v>
       </c>
       <c r="N71">
-        <v>131.70331</v>
+        <v>128.6443</v>
       </c>
       <c r="O71">
-        <v>22.3895627</v>
+        <v>21.869531</v>
       </c>
       <c r="P71">
-        <v>109.3137473</v>
+        <v>106.774769</v>
       </c>
       <c r="Q71">
-        <v>189.4137473</v>
+        <v>186.874769</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.09812751828508509</v>
+        <v>0.09976763158052787</v>
       </c>
       <c r="T71">
-        <v>1.208487720209817</v>
+        <v>1.246365625416348</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.623974299916772</v>
+        <v>1.600774667060819</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08222028947415835</v>
+        <v>0.08247804827994035</v>
       </c>
       <c r="C72">
-        <v>360.4166614294004</v>
+        <v>319.4345944077386</v>
       </c>
       <c r="D72">
-        <v>2344.546661429401</v>
+        <v>2337.553594407739</v>
       </c>
       <c r="E72">
-        <v>-721.4699999999998</v>
+        <v>-687.4809999999998</v>
       </c>
       <c r="F72">
-        <v>2379.23</v>
+        <v>2413.219</v>
       </c>
       <c r="G72">
         <v>395.1</v>
@@ -7191,28 +7191,28 @@
         <v>342.775</v>
       </c>
       <c r="M72">
-        <v>214.1307</v>
+        <v>217.18971</v>
       </c>
       <c r="N72">
-        <v>128.6443</v>
+        <v>125.58529</v>
       </c>
       <c r="O72">
-        <v>21.869531</v>
+        <v>21.3494993</v>
       </c>
       <c r="P72">
-        <v>106.774769</v>
+        <v>104.2357907</v>
       </c>
       <c r="Q72">
-        <v>186.874769</v>
+        <v>184.3357907</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.09976763158052787</v>
+        <v>0.1015208561377254</v>
       </c>
       <c r="T72">
-        <v>1.246365625416348</v>
+        <v>1.286855799947468</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.600774667060819</v>
+        <v>1.578228544989539</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08247804827994033</v>
+        <v>0.08273580708572233</v>
       </c>
       <c r="C73">
-        <v>319.43459440774</v>
+        <v>278.4941196975137</v>
       </c>
       <c r="D73">
-        <v>2337.55359440774</v>
+        <v>2330.602119697513</v>
       </c>
       <c r="E73">
-        <v>-687.4810000000002</v>
+        <v>-653.4920000000002</v>
       </c>
       <c r="F73">
-        <v>2413.219</v>
+        <v>2447.208</v>
       </c>
       <c r="G73">
         <v>395.1</v>
@@ -7273,28 +7273,28 @@
         <v>342.775</v>
       </c>
       <c r="M73">
-        <v>217.18971</v>
+        <v>220.24872</v>
       </c>
       <c r="N73">
-        <v>125.58529</v>
+        <v>122.52628</v>
       </c>
       <c r="O73">
-        <v>21.34949930000001</v>
+        <v>20.8294676</v>
       </c>
       <c r="P73">
-        <v>104.2357907</v>
+        <v>101.6968124</v>
       </c>
       <c r="Q73">
-        <v>184.3357907</v>
+        <v>181.7968124</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1015208561377253</v>
+        <v>0.1033993110204369</v>
       </c>
       <c r="T73">
-        <v>1.286855799947467</v>
+        <v>1.330238129802238</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.578228544989539</v>
+        <v>1.556308704086907</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08273580708572233</v>
+        <v>0.08299356589150431</v>
       </c>
       <c r="C74">
-        <v>278.4941196975137</v>
+        <v>237.5948673342</v>
       </c>
       <c r="D74">
-        <v>2330.602119697513</v>
+        <v>2323.6918673342</v>
       </c>
       <c r="E74">
-        <v>-653.4920000000002</v>
+        <v>-619.5030000000002</v>
       </c>
       <c r="F74">
-        <v>2447.208</v>
+        <v>2481.197</v>
       </c>
       <c r="G74">
         <v>395.1</v>
@@ -7355,28 +7355,28 @@
         <v>342.775</v>
       </c>
       <c r="M74">
-        <v>220.24872</v>
+        <v>223.30773</v>
       </c>
       <c r="N74">
-        <v>122.52628</v>
+        <v>119.46727</v>
       </c>
       <c r="O74">
-        <v>20.8294676</v>
+        <v>20.3094359</v>
       </c>
       <c r="P74">
-        <v>101.6968124</v>
+        <v>99.1578341</v>
       </c>
       <c r="Q74">
-        <v>181.7968124</v>
+        <v>179.2578341</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1033993110204369</v>
+        <v>0.1054169107092753</v>
       </c>
       <c r="T74">
-        <v>1.330238129802238</v>
+        <v>1.376833965572177</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.556308704086907</v>
+        <v>1.534989406770648</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08299356589150431</v>
+        <v>0.0832513246972863</v>
       </c>
       <c r="C75">
-        <v>237.5948673342</v>
+        <v>196.7364717280902</v>
       </c>
       <c r="D75">
-        <v>2323.6918673342</v>
+        <v>2316.82247172809</v>
       </c>
       <c r="E75">
-        <v>-619.5030000000002</v>
+        <v>-585.5140000000001</v>
       </c>
       <c r="F75">
-        <v>2481.197</v>
+        <v>2515.186</v>
       </c>
       <c r="G75">
         <v>395.1</v>
@@ -7437,28 +7437,28 @@
         <v>342.775</v>
       </c>
       <c r="M75">
-        <v>223.30773</v>
+        <v>226.36674</v>
       </c>
       <c r="N75">
-        <v>119.46727</v>
+        <v>116.40826</v>
       </c>
       <c r="O75">
-        <v>20.3094359</v>
+        <v>19.7894042</v>
       </c>
       <c r="P75">
-        <v>99.1578341</v>
+        <v>96.61885580000001</v>
       </c>
       <c r="Q75">
-        <v>179.2578341</v>
+        <v>176.7188558</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1054169107092753</v>
+        <v>0.1075897103741781</v>
       </c>
       <c r="T75">
-        <v>1.376833965572177</v>
+        <v>1.427014096401342</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.534989406770648</v>
+        <v>1.514246306679153</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0832513246972863</v>
+        <v>0.120636665844875</v>
       </c>
       <c r="C76">
-        <v>196.7364717280902</v>
+        <v>-532.5285150716459</v>
       </c>
       <c r="D76">
-        <v>2316.82247172809</v>
+        <v>1621.546484928354</v>
       </c>
       <c r="E76">
-        <v>-585.5140000000001</v>
+        <v>-551.5250000000001</v>
       </c>
       <c r="F76">
-        <v>2515.186</v>
+        <v>2549.175</v>
       </c>
       <c r="G76">
         <v>395.1</v>
@@ -7519,45 +7519,45 @@
         <v>342.775</v>
       </c>
       <c r="M76">
-        <v>226.36674</v>
+        <v>374.21889</v>
       </c>
       <c r="N76">
-        <v>116.40826</v>
+        <v>-31.44389000000001</v>
       </c>
       <c r="O76">
-        <v>19.7894042</v>
+        <v>-5.345461300000002</v>
       </c>
       <c r="P76">
-        <v>96.61885580000001</v>
+        <v>-26.09842870000001</v>
       </c>
       <c r="Q76">
-        <v>176.7188558</v>
+        <v>54.00157130000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1075897103741781</v>
+        <v>0.1107238501163853</v>
       </c>
       <c r="T76">
-        <v>1.427014096401342</v>
+        <v>1.499396076590884</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.17</v>
+        <v>0.1557156828721287</v>
       </c>
       <c r="W76">
-        <v>0.07469999999999999</v>
+        <v>0.1239409377543715</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.514246306679153</v>
+        <v>0.9159746051301686</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.120636665844875</v>
+        <v>0.121646665844875</v>
       </c>
       <c r="C77">
-        <v>-532.5285150716459</v>
+        <v>-579.5584004010689</v>
       </c>
       <c r="D77">
-        <v>1621.546484928354</v>
+        <v>1608.505599598931</v>
       </c>
       <c r="E77">
-        <v>-551.5250000000001</v>
+        <v>-517.5360000000001</v>
       </c>
       <c r="F77">
-        <v>2549.175</v>
+        <v>2583.164</v>
       </c>
       <c r="G77">
         <v>395.1</v>
@@ -7601,37 +7601,37 @@
         <v>342.775</v>
       </c>
       <c r="M77">
-        <v>374.21889</v>
+        <v>379.2084752</v>
       </c>
       <c r="N77">
-        <v>-31.44389000000001</v>
+        <v>-36.43347520000003</v>
       </c>
       <c r="O77">
-        <v>-5.345461300000002</v>
+        <v>-6.193690784000006</v>
       </c>
       <c r="P77">
-        <v>-26.09842870000001</v>
+        <v>-30.23978441600003</v>
       </c>
       <c r="Q77">
-        <v>54.00157130000002</v>
+        <v>49.860215584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1107238501163853</v>
+        <v>0.1134290105379013</v>
       </c>
       <c r="T77">
-        <v>1.499396076590884</v>
+        <v>1.561870913115504</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1557156828721287</v>
+        <v>0.1536667923080217</v>
       </c>
       <c r="W77">
-        <v>0.1239409377543715</v>
+        <v>0.1242417148891824</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9159746051301686</v>
+        <v>0.9039223076942453</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.121646665844875</v>
+        <v>0.1226566658448749</v>
       </c>
       <c r="C78">
-        <v>-579.5584004010689</v>
+        <v>-626.3802030139964</v>
       </c>
       <c r="D78">
-        <v>1608.505599598931</v>
+        <v>1595.672796986003</v>
       </c>
       <c r="E78">
-        <v>-517.5360000000001</v>
+        <v>-483.547</v>
       </c>
       <c r="F78">
-        <v>2583.164</v>
+        <v>2617.153</v>
       </c>
       <c r="G78">
         <v>395.1</v>
@@ -7683,37 +7683,37 @@
         <v>342.775</v>
       </c>
       <c r="M78">
-        <v>379.2084752</v>
+        <v>384.1980604</v>
       </c>
       <c r="N78">
-        <v>-36.43347520000003</v>
+        <v>-41.42306040000005</v>
       </c>
       <c r="O78">
-        <v>-6.193690784000006</v>
+        <v>-7.04192026800001</v>
       </c>
       <c r="P78">
-        <v>-30.23978441600003</v>
+        <v>-34.38114013200004</v>
       </c>
       <c r="Q78">
-        <v>49.860215584</v>
+        <v>45.71885986799998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1134290105379013</v>
+        <v>0.1163694023004188</v>
       </c>
       <c r="T78">
-        <v>1.561870913115504</v>
+        <v>1.629778344120526</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1536667923080217</v>
+        <v>0.1516711196806448</v>
       </c>
       <c r="W78">
-        <v>0.1242417148891824</v>
+        <v>0.1245346796308813</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9039223076942453</v>
+        <v>0.8921830569449692</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1226566658448749</v>
+        <v>0.123666665844875</v>
       </c>
       <c r="C79">
-        <v>-626.3802030139964</v>
+        <v>-672.998863799558</v>
       </c>
       <c r="D79">
-        <v>1595.672796986003</v>
+        <v>1583.043136200442</v>
       </c>
       <c r="E79">
-        <v>-483.547</v>
+        <v>-449.558</v>
       </c>
       <c r="F79">
-        <v>2617.153</v>
+        <v>2651.142</v>
       </c>
       <c r="G79">
         <v>395.1</v>
@@ -7765,37 +7765,37 @@
         <v>342.775</v>
       </c>
       <c r="M79">
-        <v>384.1980604</v>
+        <v>389.1876456</v>
       </c>
       <c r="N79">
-        <v>-41.42306040000005</v>
+        <v>-46.41264560000002</v>
       </c>
       <c r="O79">
-        <v>-7.04192026800001</v>
+        <v>-7.890149752000004</v>
       </c>
       <c r="P79">
-        <v>-34.38114013200004</v>
+        <v>-38.52249584800001</v>
       </c>
       <c r="Q79">
-        <v>45.71885986799998</v>
+        <v>41.57750415200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1163694023004188</v>
+        <v>0.1195771024049833</v>
       </c>
       <c r="T79">
-        <v>1.629778344120526</v>
+        <v>1.703859177944186</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1516711196806448</v>
+        <v>0.1497266181462776</v>
       </c>
       <c r="W79">
-        <v>0.1245346796308813</v>
+        <v>0.1248201324561265</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8921830569449692</v>
+        <v>0.880744812625162</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.123666665844875</v>
+        <v>0.124676665844875</v>
       </c>
       <c r="C80">
-        <v>-672.998863799558</v>
+        <v>-719.4191684478301</v>
       </c>
       <c r="D80">
-        <v>1583.043136200442</v>
+        <v>1570.61183155217</v>
       </c>
       <c r="E80">
-        <v>-449.558</v>
+        <v>-415.569</v>
       </c>
       <c r="F80">
-        <v>2651.142</v>
+        <v>2685.131</v>
       </c>
       <c r="G80">
         <v>395.1</v>
@@ -7847,37 +7847,37 @@
         <v>342.775</v>
       </c>
       <c r="M80">
-        <v>389.1876456</v>
+        <v>394.1772308</v>
       </c>
       <c r="N80">
-        <v>-46.41264560000002</v>
+        <v>-51.40223080000004</v>
       </c>
       <c r="O80">
-        <v>-7.890149752000004</v>
+        <v>-8.738379236000007</v>
       </c>
       <c r="P80">
-        <v>-38.52249584800001</v>
+        <v>-42.66385156400003</v>
       </c>
       <c r="Q80">
-        <v>41.57750415200001</v>
+        <v>37.43614843599999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1195771024049833</v>
+        <v>0.1230902977576015</v>
       </c>
       <c r="T80">
-        <v>1.703859177944186</v>
+        <v>1.784995329274862</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1497266181462776</v>
+        <v>0.1478313444988563</v>
       </c>
       <c r="W80">
-        <v>0.1248201324561265</v>
+        <v>0.1250983586275679</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.880744812625162</v>
+        <v>0.8695961441109195</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.124676665844875</v>
+        <v>0.125686665844875</v>
       </c>
       <c r="C81">
-        <v>-719.4191684478301</v>
+        <v>-765.6457534960869</v>
       </c>
       <c r="D81">
-        <v>1570.61183155217</v>
+        <v>1558.374246503913</v>
       </c>
       <c r="E81">
-        <v>-415.569</v>
+        <v>-381.5799999999999</v>
       </c>
       <c r="F81">
-        <v>2685.131</v>
+        <v>2719.12</v>
       </c>
       <c r="G81">
         <v>395.1</v>
@@ -7929,37 +7929,37 @@
         <v>342.775</v>
       </c>
       <c r="M81">
-        <v>394.1772308</v>
+        <v>399.166816</v>
       </c>
       <c r="N81">
-        <v>-51.40223080000004</v>
+        <v>-56.39181600000006</v>
       </c>
       <c r="O81">
-        <v>-8.738379236000007</v>
+        <v>-9.586608720000012</v>
       </c>
       <c r="P81">
-        <v>-42.66385156400003</v>
+        <v>-46.80520728000005</v>
       </c>
       <c r="Q81">
-        <v>37.43614843599999</v>
+        <v>33.29479271999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1230902977576015</v>
+        <v>0.1269548126454816</v>
       </c>
       <c r="T81">
-        <v>1.784995329274862</v>
+        <v>1.874245095738605</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1478313444988563</v>
+        <v>0.1459834526926206</v>
       </c>
       <c r="W81">
-        <v>0.1250983586275679</v>
+        <v>0.1253696291447233</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8695961441109195</v>
+        <v>0.858726192309533</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.125686665844875</v>
+        <v>0.126696665844875</v>
       </c>
       <c r="C82">
-        <v>-765.6457534960869</v>
+        <v>-811.6831120945717</v>
       </c>
       <c r="D82">
-        <v>1558.374246503913</v>
+        <v>1546.325887905428</v>
       </c>
       <c r="E82">
-        <v>-381.5799999999999</v>
+        <v>-347.5909999999999</v>
       </c>
       <c r="F82">
-        <v>2719.12</v>
+        <v>2753.109</v>
       </c>
       <c r="G82">
         <v>395.1</v>
@@ -8011,37 +8011,37 @@
         <v>342.775</v>
       </c>
       <c r="M82">
-        <v>399.166816</v>
+        <v>404.1564012</v>
       </c>
       <c r="N82">
-        <v>-56.39181600000006</v>
+        <v>-61.38140120000003</v>
       </c>
       <c r="O82">
-        <v>-9.586608720000012</v>
+        <v>-10.43483820400001</v>
       </c>
       <c r="P82">
-        <v>-46.80520728000005</v>
+        <v>-50.94656299600003</v>
       </c>
       <c r="Q82">
-        <v>33.29479271999998</v>
+        <v>29.153437004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1269548126454816</v>
+        <v>0.1312261185741912</v>
       </c>
       <c r="T82">
-        <v>1.874245095738605</v>
+        <v>1.97288957446169</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1459834526926206</v>
+        <v>0.1441811878445636</v>
       </c>
       <c r="W82">
-        <v>0.1253696291447233</v>
+        <v>0.1256342016244181</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.858726192309533</v>
+        <v>0.8481246343797857</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.126696665844875</v>
+        <v>0.1277066658448749</v>
       </c>
       <c r="C83">
-        <v>-811.6831120945717</v>
+        <v>-857.5355995068594</v>
       </c>
       <c r="D83">
-        <v>1546.325887905428</v>
+        <v>1534.46240049314</v>
       </c>
       <c r="E83">
-        <v>-347.5909999999999</v>
+        <v>-313.6019999999999</v>
       </c>
       <c r="F83">
-        <v>2753.109</v>
+        <v>2787.098</v>
       </c>
       <c r="G83">
         <v>395.1</v>
@@ -8093,37 +8093,37 @@
         <v>342.775</v>
       </c>
       <c r="M83">
-        <v>404.1564012</v>
+        <v>409.1459864</v>
       </c>
       <c r="N83">
-        <v>-61.38140120000003</v>
+        <v>-66.37098640000005</v>
       </c>
       <c r="O83">
-        <v>-10.43483820400001</v>
+        <v>-11.28306768800001</v>
       </c>
       <c r="P83">
-        <v>-50.94656299600003</v>
+        <v>-55.08791871200004</v>
       </c>
       <c r="Q83">
-        <v>29.153437004</v>
+        <v>25.01208128799998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1312261185741912</v>
+        <v>0.1359720140505351</v>
       </c>
       <c r="T83">
-        <v>1.97288957446169</v>
+        <v>2.082494550820673</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1441811878445636</v>
+        <v>0.1424228806757274</v>
       </c>
       <c r="W83">
-        <v>0.1256342016244181</v>
+        <v>0.1258923211168032</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8481246343797857</v>
+        <v>0.8377816510336906</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1277066658448749</v>
+        <v>0.128716665844875</v>
       </c>
       <c r="C84">
-        <v>-857.5355995068594</v>
+        <v>-903.207438358952</v>
       </c>
       <c r="D84">
-        <v>1534.46240049314</v>
+        <v>1522.779561641048</v>
       </c>
       <c r="E84">
-        <v>-313.6019999999999</v>
+        <v>-279.6129999999998</v>
       </c>
       <c r="F84">
-        <v>2787.098</v>
+        <v>2821.087</v>
       </c>
       <c r="G84">
         <v>395.1</v>
@@ -8175,37 +8175,37 @@
         <v>342.775</v>
       </c>
       <c r="M84">
-        <v>409.1459864</v>
+        <v>414.1355716</v>
       </c>
       <c r="N84">
-        <v>-66.37098640000005</v>
+        <v>-71.36057160000007</v>
       </c>
       <c r="O84">
-        <v>-11.28306768800001</v>
+        <v>-12.13129717200001</v>
       </c>
       <c r="P84">
-        <v>-55.08791871200004</v>
+        <v>-59.22927442800006</v>
       </c>
       <c r="Q84">
-        <v>25.01208128799998</v>
+        <v>20.87072557199996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1359720140505351</v>
+        <v>0.1412762501711548</v>
       </c>
       <c r="T84">
-        <v>2.082494550820673</v>
+        <v>2.204994230280712</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1424228806757274</v>
+        <v>0.1407069423543331</v>
       </c>
       <c r="W84">
-        <v>0.1258923211168032</v>
+        <v>0.1261442208623839</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8377816510336906</v>
+        <v>0.8276878962019594</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.128716665844875</v>
+        <v>0.129726665844875</v>
       </c>
       <c r="C85">
-        <v>-903.207438358952</v>
+        <v>-948.7027236503955</v>
       </c>
       <c r="D85">
-        <v>1522.779561641048</v>
+        <v>1511.273276349605</v>
       </c>
       <c r="E85">
-        <v>-279.6129999999998</v>
+        <v>-245.6239999999998</v>
       </c>
       <c r="F85">
-        <v>2821.087</v>
+        <v>2855.076</v>
       </c>
       <c r="G85">
         <v>395.1</v>
@@ -8257,37 +8257,37 @@
         <v>342.775</v>
       </c>
       <c r="M85">
-        <v>414.1355716</v>
+        <v>419.1251568000001</v>
       </c>
       <c r="N85">
-        <v>-71.36057160000007</v>
+        <v>-76.35015680000009</v>
       </c>
       <c r="O85">
-        <v>-12.13129717200001</v>
+        <v>-12.97952665600002</v>
       </c>
       <c r="P85">
-        <v>-59.22927442800006</v>
+        <v>-63.37063014400007</v>
       </c>
       <c r="Q85">
-        <v>20.87072557199996</v>
+        <v>16.72936985599995</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1412762501711548</v>
+        <v>0.147243515806852</v>
       </c>
       <c r="T85">
-        <v>2.204994230280712</v>
+        <v>2.342806369673258</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1407069423543331</v>
+        <v>0.1390318597072577</v>
       </c>
       <c r="W85">
-        <v>0.1261442208623839</v>
+        <v>0.1263901229949746</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8276878962019594</v>
+        <v>0.8178344688662218</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1297266658448749</v>
+        <v>0.1307366658448749</v>
       </c>
       <c r="C86">
-        <v>-948.7027236503945</v>
+        <v>-994.0254275399134</v>
       </c>
       <c r="D86">
-        <v>1511.273276349605</v>
+        <v>1499.939572460086</v>
       </c>
       <c r="E86">
-        <v>-245.6240000000003</v>
+        <v>-211.6350000000002</v>
       </c>
       <c r="F86">
-        <v>2855.076</v>
+        <v>2889.065</v>
       </c>
       <c r="G86">
         <v>395.1</v>
@@ -8339,37 +8339,37 @@
         <v>342.775</v>
       </c>
       <c r="M86">
-        <v>419.1251568</v>
+        <v>424.114742</v>
       </c>
       <c r="N86">
-        <v>-76.35015679999998</v>
+        <v>-81.339742</v>
       </c>
       <c r="O86">
-        <v>-12.979526656</v>
+        <v>-13.82775614</v>
       </c>
       <c r="P86">
-        <v>-63.37063014399998</v>
+        <v>-67.51198586</v>
       </c>
       <c r="Q86">
-        <v>16.72936985600004</v>
+        <v>12.58801414000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.147243515806852</v>
+        <v>0.1540064168606421</v>
       </c>
       <c r="T86">
-        <v>2.342806369673256</v>
+        <v>2.498993460984806</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1390318597072578</v>
+        <v>0.1373961907695253</v>
       </c>
       <c r="W86">
-        <v>0.1263901229949746</v>
+        <v>0.1266302391950337</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.817834468866222</v>
+        <v>0.8082128868795605</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1307366658448749</v>
+        <v>0.1787638340180694</v>
       </c>
       <c r="C87">
-        <v>-994.0254275399134</v>
+        <v>-1422.301887817016</v>
       </c>
       <c r="D87">
-        <v>1499.939572460086</v>
+        <v>1105.652112182984</v>
       </c>
       <c r="E87">
-        <v>-211.6350000000002</v>
+        <v>-177.6460000000002</v>
       </c>
       <c r="F87">
-        <v>2889.065</v>
+        <v>2923.054</v>
       </c>
       <c r="G87">
         <v>395.1</v>
@@ -8421,45 +8421,45 @@
         <v>342.775</v>
       </c>
       <c r="M87">
-        <v>424.114742</v>
+        <v>586.9492432</v>
       </c>
       <c r="N87">
-        <v>-81.339742</v>
+        <v>-244.1742432</v>
       </c>
       <c r="O87">
-        <v>-13.82775614</v>
+        <v>-41.509621344</v>
       </c>
       <c r="P87">
-        <v>-67.51198586</v>
+        <v>-202.664621856</v>
       </c>
       <c r="Q87">
-        <v>12.58801414000003</v>
+        <v>-122.564621856</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1540064168606421</v>
+        <v>0.1658580764449338</v>
       </c>
       <c r="T87">
-        <v>2.498993460984806</v>
+        <v>2.772703843993852</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1373961907695253</v>
+        <v>0.09927902740330173</v>
       </c>
       <c r="W87">
-        <v>0.1266302391950337</v>
+        <v>0.180864771297417</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8082128868795605</v>
+        <v>0.5839942788429513</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1787638340180694</v>
+        <v>0.1803138340180694</v>
       </c>
       <c r="C88">
-        <v>-1422.301887817016</v>
+        <v>-1465.591971430383</v>
       </c>
       <c r="D88">
-        <v>1105.652112182984</v>
+        <v>1096.351028569617</v>
       </c>
       <c r="E88">
-        <v>-177.6460000000002</v>
+        <v>-143.6570000000002</v>
       </c>
       <c r="F88">
-        <v>2923.054</v>
+        <v>2957.043</v>
       </c>
       <c r="G88">
         <v>395.1</v>
@@ -8503,37 +8503,37 @@
         <v>342.775</v>
       </c>
       <c r="M88">
-        <v>586.9492432</v>
+        <v>593.7742344</v>
       </c>
       <c r="N88">
-        <v>-244.1742432</v>
+        <v>-250.9992344</v>
       </c>
       <c r="O88">
-        <v>-41.509621344</v>
+        <v>-42.669869848</v>
       </c>
       <c r="P88">
-        <v>-202.664621856</v>
+        <v>-208.329364552</v>
       </c>
       <c r="Q88">
-        <v>-122.564621856</v>
+        <v>-128.229364552</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1658580764449338</v>
+        <v>0.1750933130945441</v>
       </c>
       <c r="T88">
-        <v>2.772703843993852</v>
+        <v>2.985988755070303</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.09927902740330173</v>
+        <v>0.09813788915728675</v>
       </c>
       <c r="W88">
-        <v>0.180864771297417</v>
+        <v>0.1810939118572168</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5839942788429513</v>
+        <v>0.5772817009252162</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1803138340180694</v>
+        <v>0.1818638340180694</v>
       </c>
       <c r="C89">
-        <v>-1465.591971430383</v>
+        <v>-1508.72687336131</v>
       </c>
       <c r="D89">
-        <v>1096.351028569617</v>
+        <v>1087.20512663869</v>
       </c>
       <c r="E89">
-        <v>-143.6570000000002</v>
+        <v>-109.6680000000001</v>
       </c>
       <c r="F89">
-        <v>2957.043</v>
+        <v>2991.032</v>
       </c>
       <c r="G89">
         <v>395.1</v>
@@ -8585,37 +8585,37 @@
         <v>342.775</v>
       </c>
       <c r="M89">
-        <v>593.7742344</v>
+        <v>600.5992256</v>
       </c>
       <c r="N89">
-        <v>-250.9992344</v>
+        <v>-257.8242256</v>
       </c>
       <c r="O89">
-        <v>-42.669869848</v>
+        <v>-43.830118352</v>
       </c>
       <c r="P89">
-        <v>-208.329364552</v>
+        <v>-213.994107248</v>
       </c>
       <c r="Q89">
-        <v>-128.229364552</v>
+        <v>-133.894107248</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1750933130945441</v>
+        <v>0.1858677558524228</v>
       </c>
       <c r="T89">
-        <v>2.985988755070303</v>
+        <v>3.234821151326161</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09813788915728675</v>
+        <v>0.09702268587140848</v>
       </c>
       <c r="W89">
-        <v>0.1810939118572168</v>
+        <v>0.1813178446770212</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5772817009252162</v>
+        <v>0.5707216815965206</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1818638340180694</v>
+        <v>0.1834138340180694</v>
       </c>
       <c r="C90">
-        <v>-1508.72687336131</v>
+        <v>-1551.710445116961</v>
       </c>
       <c r="D90">
-        <v>1087.20512663869</v>
+        <v>1078.210554883039</v>
       </c>
       <c r="E90">
-        <v>-109.6680000000001</v>
+        <v>-75.67900000000009</v>
       </c>
       <c r="F90">
-        <v>2991.032</v>
+        <v>3025.021</v>
       </c>
       <c r="G90">
         <v>395.1</v>
@@ -8667,37 +8667,37 @@
         <v>342.775</v>
       </c>
       <c r="M90">
-        <v>600.5992256</v>
+        <v>607.4242168</v>
       </c>
       <c r="N90">
-        <v>-257.8242256</v>
+        <v>-264.6492168</v>
       </c>
       <c r="O90">
-        <v>-43.830118352</v>
+        <v>-44.990366856</v>
       </c>
       <c r="P90">
-        <v>-213.994107248</v>
+        <v>-219.658849944</v>
       </c>
       <c r="Q90">
-        <v>-133.894107248</v>
+        <v>-139.5588499439999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1858677558524228</v>
+        <v>0.1986011882026431</v>
       </c>
       <c r="T90">
-        <v>3.234821151326161</v>
+        <v>3.528895801446722</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09702268587140848</v>
+        <v>0.09593254333352749</v>
       </c>
       <c r="W90">
-        <v>0.1813178446770212</v>
+        <v>0.1815367452986277</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5707216815965206</v>
+        <v>0.5643090784325147</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1834138340180694</v>
+        <v>0.1849638340180694</v>
       </c>
       <c r="C91">
-        <v>-1551.710445116961</v>
+        <v>-1594.546411794475</v>
       </c>
       <c r="D91">
-        <v>1078.210554883039</v>
+        <v>1069.363588205525</v>
       </c>
       <c r="E91">
-        <v>-75.67900000000009</v>
+        <v>-41.69000000000005</v>
       </c>
       <c r="F91">
-        <v>3025.021</v>
+        <v>3059.01</v>
       </c>
       <c r="G91">
         <v>395.1</v>
@@ -8749,37 +8749,37 @@
         <v>342.775</v>
       </c>
       <c r="M91">
-        <v>607.4242168</v>
+        <v>614.249208</v>
       </c>
       <c r="N91">
-        <v>-264.6492168</v>
+        <v>-271.474208</v>
       </c>
       <c r="O91">
-        <v>-44.990366856</v>
+        <v>-46.15061536</v>
       </c>
       <c r="P91">
-        <v>-219.658849944</v>
+        <v>-225.32359264</v>
       </c>
       <c r="Q91">
-        <v>-139.5588499439999</v>
+        <v>-145.22359264</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.1986011882026431</v>
+        <v>0.2138813070229074</v>
       </c>
       <c r="T91">
-        <v>3.528895801446722</v>
+        <v>3.881785381591394</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09593254333352749</v>
+        <v>0.0948666261853772</v>
       </c>
       <c r="W91">
-        <v>0.1815367452986277</v>
+        <v>0.1817507814619763</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5643090784325147</v>
+        <v>0.5580389775610424</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1849638340180694</v>
+        <v>0.1865138340180694</v>
       </c>
       <c r="C92">
-        <v>-1594.546411794475</v>
+        <v>-1637.238377224878</v>
       </c>
       <c r="D92">
-        <v>1069.363588205525</v>
+        <v>1060.660622775122</v>
       </c>
       <c r="E92">
-        <v>-41.69000000000005</v>
+        <v>-7.701000000000022</v>
       </c>
       <c r="F92">
-        <v>3059.01</v>
+        <v>3092.999</v>
       </c>
       <c r="G92">
         <v>395.1</v>
@@ -8831,37 +8831,37 @@
         <v>342.775</v>
       </c>
       <c r="M92">
-        <v>614.249208</v>
+        <v>621.0741992</v>
       </c>
       <c r="N92">
-        <v>-271.474208</v>
+        <v>-278.2991992</v>
       </c>
       <c r="O92">
-        <v>-46.15061536</v>
+        <v>-47.310863864</v>
       </c>
       <c r="P92">
-        <v>-225.32359264</v>
+        <v>-230.988335336</v>
       </c>
       <c r="Q92">
-        <v>-145.22359264</v>
+        <v>-150.888335336</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2138813070229074</v>
+        <v>0.2325570078032304</v>
       </c>
       <c r="T92">
-        <v>3.881785381591394</v>
+        <v>4.313094868434883</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.0948666261853772</v>
+        <v>0.09382413578773569</v>
       </c>
       <c r="W92">
-        <v>0.1817507814619763</v>
+        <v>0.1819601135338227</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5580389775610424</v>
+        <v>0.5519066811043276</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1865138340180694</v>
+        <v>0.1880638340180694</v>
       </c>
       <c r="C93">
-        <v>-1637.238377224878</v>
+        <v>-1679.789828867839</v>
       </c>
       <c r="D93">
-        <v>1060.660622775122</v>
+        <v>1052.098171132161</v>
       </c>
       <c r="E93">
-        <v>-7.701000000000022</v>
+        <v>26.28800000000001</v>
       </c>
       <c r="F93">
-        <v>3092.999</v>
+        <v>3126.988</v>
       </c>
       <c r="G93">
         <v>395.1</v>
@@ -8913,37 +8913,37 @@
         <v>342.775</v>
       </c>
       <c r="M93">
-        <v>621.0741992</v>
+        <v>627.8991904</v>
       </c>
       <c r="N93">
-        <v>-278.2991992</v>
+        <v>-285.1241904</v>
       </c>
       <c r="O93">
-        <v>-47.310863864</v>
+        <v>-48.471112368</v>
       </c>
       <c r="P93">
-        <v>-230.988335336</v>
+        <v>-236.653078032</v>
       </c>
       <c r="Q93">
-        <v>-150.888335336</v>
+        <v>-156.5530780319999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2325570078032304</v>
+        <v>0.2559016337786342</v>
       </c>
       <c r="T93">
-        <v>4.313094868434883</v>
+        <v>4.852231726989244</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09382413578773569</v>
+        <v>0.09280430822482552</v>
       </c>
       <c r="W93">
-        <v>0.1819601135338227</v>
+        <v>0.182164894908455</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5519066811043276</v>
+        <v>0.5459076954401501</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1880638340180694</v>
+        <v>0.1896138340180694</v>
       </c>
       <c r="C94">
-        <v>-1679.789828867839</v>
+        <v>-1722.204142471242</v>
       </c>
       <c r="D94">
-        <v>1052.098171132161</v>
+        <v>1043.672857528758</v>
       </c>
       <c r="E94">
-        <v>26.28800000000001</v>
+        <v>60.27700000000004</v>
       </c>
       <c r="F94">
-        <v>3126.988</v>
+        <v>3160.977</v>
       </c>
       <c r="G94">
         <v>395.1</v>
@@ -8995,37 +8995,37 @@
         <v>342.775</v>
       </c>
       <c r="M94">
-        <v>627.8991904</v>
+        <v>634.7241816</v>
       </c>
       <c r="N94">
-        <v>-285.1241904</v>
+        <v>-291.9491816</v>
       </c>
       <c r="O94">
-        <v>-48.471112368</v>
+        <v>-49.631360872</v>
       </c>
       <c r="P94">
-        <v>-236.653078032</v>
+        <v>-242.317820728</v>
       </c>
       <c r="Q94">
-        <v>-156.5530780319999</v>
+        <v>-162.2178207279999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2559016337786342</v>
+        <v>0.2859161528898678</v>
       </c>
       <c r="T94">
-        <v>4.852231726989244</v>
+        <v>5.545407687987709</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09280430822482552</v>
+        <v>0.09180641243746181</v>
       </c>
       <c r="W94">
-        <v>0.182164894908455</v>
+        <v>0.1823652723825577</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5459076954401501</v>
+        <v>0.5400377202203634</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1896138340180694</v>
+        <v>0.1911638340180694</v>
       </c>
       <c r="C95">
-        <v>-1722.204142471242</v>
+        <v>-1764.484586508648</v>
       </c>
       <c r="D95">
-        <v>1043.672857528758</v>
+        <v>1035.381413491352</v>
       </c>
       <c r="E95">
-        <v>60.27700000000004</v>
+        <v>94.26600000000008</v>
       </c>
       <c r="F95">
-        <v>3160.977</v>
+        <v>3194.966</v>
       </c>
       <c r="G95">
         <v>395.1</v>
@@ -9077,37 +9077,37 @@
         <v>342.775</v>
       </c>
       <c r="M95">
-        <v>634.7241816</v>
+        <v>641.5491728</v>
       </c>
       <c r="N95">
-        <v>-291.9491816</v>
+        <v>-298.7741728</v>
       </c>
       <c r="O95">
-        <v>-49.631360872</v>
+        <v>-50.791609376</v>
       </c>
       <c r="P95">
-        <v>-242.317820728</v>
+        <v>-247.982563424</v>
       </c>
       <c r="Q95">
-        <v>-162.2178207279999</v>
+        <v>-167.882563424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2859161528898678</v>
+        <v>0.3259355117048458</v>
       </c>
       <c r="T95">
-        <v>5.545407687987709</v>
+        <v>6.469642302652328</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09180641243746181</v>
+        <v>0.09082974847536114</v>
       </c>
       <c r="W95">
-        <v>0.1823652723825577</v>
+        <v>0.1825613865061475</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5400377202203634</v>
+        <v>0.5342926380903597</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1911638340180694</v>
+        <v>0.1927138340180694</v>
       </c>
       <c r="C96">
-        <v>-1764.484586508648</v>
+        <v>-1806.634326406906</v>
       </c>
       <c r="D96">
-        <v>1035.381413491352</v>
+        <v>1027.220673593094</v>
       </c>
       <c r="E96">
-        <v>94.26600000000008</v>
+        <v>128.2550000000001</v>
       </c>
       <c r="F96">
-        <v>3194.966</v>
+        <v>3228.955</v>
       </c>
       <c r="G96">
         <v>395.1</v>
@@ -9159,37 +9159,37 @@
         <v>342.775</v>
       </c>
       <c r="M96">
-        <v>641.5491728</v>
+        <v>648.374164</v>
       </c>
       <c r="N96">
-        <v>-298.7741728</v>
+        <v>-305.599164</v>
       </c>
       <c r="O96">
-        <v>-50.791609376</v>
+        <v>-51.95185788</v>
       </c>
       <c r="P96">
-        <v>-247.982563424</v>
+        <v>-253.64730612</v>
       </c>
       <c r="Q96">
-        <v>-167.882563424</v>
+        <v>-173.5473061199999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3259355117048458</v>
+        <v>0.3819626140458151</v>
       </c>
       <c r="T96">
-        <v>6.469642302652328</v>
+        <v>7.763570763182797</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09082974847536114</v>
+        <v>0.08987364585983104</v>
       </c>
       <c r="W96">
-        <v>0.1825613865061475</v>
+        <v>0.1827533719113459</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5342926380903597</v>
+        <v>0.5286685050578295</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1927138340180694</v>
+        <v>0.1942638340180694</v>
       </c>
       <c r="C97">
-        <v>-1806.634326406906</v>
+        <v>-1848.656428575397</v>
       </c>
       <c r="D97">
-        <v>1027.220673593094</v>
+        <v>1019.187571424603</v>
       </c>
       <c r="E97">
-        <v>128.2550000000001</v>
+        <v>162.2440000000001</v>
       </c>
       <c r="F97">
-        <v>3228.955</v>
+        <v>3262.944</v>
       </c>
       <c r="G97">
         <v>395.1</v>
@@ -9241,37 +9241,37 @@
         <v>342.775</v>
       </c>
       <c r="M97">
-        <v>648.374164</v>
+        <v>655.1991552000001</v>
       </c>
       <c r="N97">
-        <v>-305.599164</v>
+        <v>-312.4241552000001</v>
       </c>
       <c r="O97">
-        <v>-51.95185788</v>
+        <v>-53.11210638400002</v>
       </c>
       <c r="P97">
-        <v>-253.64730612</v>
+        <v>-259.3120488160001</v>
       </c>
       <c r="Q97">
-        <v>-173.5473061199999</v>
+        <v>-179.212048816</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.3819626140458151</v>
+        <v>0.4660032675572691</v>
       </c>
       <c r="T97">
-        <v>7.763570763182797</v>
+        <v>9.704463453978502</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08987364585983104</v>
+        <v>0.0889374620487911</v>
       </c>
       <c r="W97">
-        <v>0.1827533719113459</v>
+        <v>0.1829413576206028</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5286685050578295</v>
+        <v>0.523161541463477</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1942638340180693</v>
+        <v>0.1958138340180694</v>
       </c>
       <c r="C98">
-        <v>-1848.656428575396</v>
+        <v>-1890.553864247691</v>
       </c>
       <c r="D98">
-        <v>1019.187571424603</v>
+        <v>1011.279135752308</v>
       </c>
       <c r="E98">
-        <v>162.2439999999997</v>
+        <v>196.2329999999997</v>
       </c>
       <c r="F98">
-        <v>3262.944</v>
+        <v>3296.933</v>
       </c>
       <c r="G98">
         <v>395.1</v>
@@ -9323,37 +9323,37 @@
         <v>342.775</v>
       </c>
       <c r="M98">
-        <v>655.1991552</v>
+        <v>662.0241463999999</v>
       </c>
       <c r="N98">
-        <v>-312.4241552</v>
+        <v>-319.2491464</v>
       </c>
       <c r="O98">
-        <v>-53.112106384</v>
+        <v>-54.272354888</v>
       </c>
       <c r="P98">
-        <v>-259.312048816</v>
+        <v>-264.976791512</v>
       </c>
       <c r="Q98">
-        <v>-179.2120488159999</v>
+        <v>-184.876791512</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.466003267557268</v>
+        <v>0.6060710234096907</v>
       </c>
       <c r="T98">
-        <v>9.704463453978475</v>
+        <v>12.93928460530464</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08893746204879112</v>
+        <v>0.08802058099674173</v>
       </c>
       <c r="W98">
-        <v>0.1829413576206027</v>
+        <v>0.1831254673358543</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5231615414634772</v>
+        <v>0.5177681235102454</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1958138340180694</v>
+        <v>0.1973638340180694</v>
       </c>
       <c r="C99">
-        <v>-1890.553864247691</v>
+        <v>-1932.32951314572</v>
       </c>
       <c r="D99">
-        <v>1011.279135752308</v>
+        <v>1003.49248685428</v>
       </c>
       <c r="E99">
-        <v>196.2329999999997</v>
+        <v>230.2219999999998</v>
       </c>
       <c r="F99">
-        <v>3296.933</v>
+        <v>3330.922</v>
       </c>
       <c r="G99">
         <v>395.1</v>
@@ -9405,37 +9405,37 @@
         <v>342.775</v>
       </c>
       <c r="M99">
-        <v>662.0241463999999</v>
+        <v>668.8491375999999</v>
       </c>
       <c r="N99">
-        <v>-319.2491464</v>
+        <v>-326.0741376</v>
       </c>
       <c r="O99">
-        <v>-54.272354888</v>
+        <v>-55.432603392</v>
       </c>
       <c r="P99">
-        <v>-264.976791512</v>
+        <v>-270.641534208</v>
       </c>
       <c r="Q99">
-        <v>-184.876791512</v>
+        <v>-190.541534208</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6060710234096907</v>
+        <v>0.8862065351145358</v>
       </c>
       <c r="T99">
-        <v>12.93928460530464</v>
+        <v>19.40892690795695</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08802058099674173</v>
+        <v>0.08712241180289743</v>
       </c>
       <c r="W99">
-        <v>0.1831254673358543</v>
+        <v>0.1833058197099782</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5177681235102454</v>
+        <v>0.5124847753111612</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1973638340180694</v>
+        <v>0.1989138340180694</v>
       </c>
       <c r="C100">
-        <v>-1932.32951314572</v>
+        <v>-1973.986166975963</v>
       </c>
       <c r="D100">
-        <v>1003.49248685428</v>
+        <v>995.8248330240369</v>
       </c>
       <c r="E100">
-        <v>230.2219999999998</v>
+        <v>264.2109999999998</v>
       </c>
       <c r="F100">
-        <v>3330.922</v>
+        <v>3364.911</v>
       </c>
       <c r="G100">
         <v>395.1</v>
@@ -9487,37 +9487,37 @@
         <v>342.775</v>
       </c>
       <c r="M100">
-        <v>668.8491375999999</v>
+        <v>675.6741287999999</v>
       </c>
       <c r="N100">
-        <v>-326.0741376</v>
+        <v>-332.8991288</v>
       </c>
       <c r="O100">
-        <v>-55.432603392</v>
+        <v>-56.592851896</v>
       </c>
       <c r="P100">
-        <v>-270.641534208</v>
+        <v>-276.306276904</v>
       </c>
       <c r="Q100">
-        <v>-190.541534208</v>
+        <v>-196.2062769039999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.8862065351145358</v>
+        <v>1.726613070229072</v>
       </c>
       <c r="T100">
-        <v>19.40892690795695</v>
+        <v>38.8178538159139</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08712241180289743</v>
+        <v>0.086242387441252</v>
       </c>
       <c r="W100">
-        <v>0.1833058197099782</v>
+        <v>0.1834825286017966</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5124847753111612</v>
+        <v>0.5073081614191294</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1989138340180694</v>
-      </c>
-      <c r="C101">
-        <v>-1973.986166975963</v>
-      </c>
-      <c r="D101">
-        <v>995.8248330240369</v>
-      </c>
-      <c r="E101">
-        <v>264.2109999999998</v>
-      </c>
-      <c r="F101">
-        <v>3364.911</v>
-      </c>
-      <c r="G101">
-        <v>395.1</v>
-      </c>
-      <c r="H101">
-        <v>298.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>422.875</v>
-      </c>
-      <c r="K101">
-        <v>80.10000000000002</v>
-      </c>
-      <c r="L101">
-        <v>342.775</v>
-      </c>
-      <c r="M101">
-        <v>675.6741287999999</v>
-      </c>
-      <c r="N101">
-        <v>-332.8991288</v>
-      </c>
-      <c r="O101">
-        <v>-56.592851896</v>
-      </c>
-      <c r="P101">
-        <v>-276.306276904</v>
-      </c>
-      <c r="Q101">
-        <v>-196.2062769039999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.726613070229072</v>
-      </c>
-      <c r="T101">
-        <v>38.8178538159139</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.086242387441252</v>
-      </c>
-      <c r="W101">
-        <v>0.1834825286017966</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5073081614191294</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
